--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -690,6 +690,57 @@
       </c>
       <c r="O4" s="4" t="n">
         <v>-0.079933</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>92058.41</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>30.26</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>92058.41</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>-0.007579</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>0.000537</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP:ATSE:NO_PRICE</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>0.000329</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>-0.079416</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>-0.071837</v>
+      </c>
+      <c r="O5" s="4" t="n">
+        <v>-0.079953</v>
       </c>
     </row>
   </sheetData>
@@ -877,7 +928,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -921,11 +972,11 @@
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="5" t="n">
-        <v>34.560001</v>
+        <v>34.740002</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="K3" s="3" t="n"/>
@@ -978,11 +1029,11 @@
       </c>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="5" t="n">
-        <v>3.77</v>
+        <v>3.75</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="K4" s="3" t="n"/>
@@ -1728,7 +1779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2359,6 +2410,204 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>BRLUSD=X</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>0.194322</v>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>CHFUSD=X</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>1.22471</v>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>EURUSD=X</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>1.155402</v>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP.AT</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-09-14</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>GBPUSD=X</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>1.34991</v>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>IWDA.L</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>145.960007</v>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>LIGT3.SA</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>SAPR11.SA</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>34.740002</v>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -741,6 +741,57 @@
       </c>
       <c r="O5" s="4" t="n">
         <v>-0.079953</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>92068.5</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>92068.5</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>-0.012679</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>0.000645</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP:ATSE:NO_PRICE</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>0.00011</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>-0.079315</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>-0.066636</v>
+      </c>
+      <c r="O6" s="4" t="n">
+        <v>-0.07996</v>
       </c>
     </row>
   </sheetData>
@@ -928,7 +979,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -972,11 +1023,11 @@
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="5" t="n">
-        <v>34.740002</v>
+        <v>34.349998</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K3" s="3" t="n"/>
@@ -1029,11 +1080,11 @@
       </c>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="5" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="K4" s="3" t="n"/>
@@ -1779,7 +1830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2608,6 +2659,204 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>BRLUSD=X</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>0.194047</v>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>CHFUSD=X</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>1.222046</v>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>EURUSD=X</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>1.154068</v>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP.AT</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="n"/>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-09-15</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>GBPUSD=X</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>1.347491</v>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>IWDA.L</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>145.210007</v>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>LIGT3.SA</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>SAPR11.SA</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>34.349998</v>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -792,6 +792,57 @@
       </c>
       <c r="O6" s="4" t="n">
         <v>-0.07996</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>92078.59</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>92078.59</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>-0.008055</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>0.000752</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP:ATSE:NO_PRICE</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>0.00011</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>-0.07921400000000001</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>-0.071159</v>
+      </c>
+      <c r="O7" s="4" t="n">
+        <v>-0.079966</v>
       </c>
     </row>
   </sheetData>
@@ -979,7 +1030,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -1023,11 +1074,11 @@
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="5" t="n">
-        <v>34.349998</v>
+        <v>34.099998</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K3" s="3" t="n"/>
@@ -1080,11 +1131,11 @@
       </c>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="5" t="n">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="K4" s="3" t="n"/>
@@ -1830,7 +1881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2857,6 +2908,204 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>BRLUSD=X</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>0.194194</v>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>CHFUSD=X</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>1.212004</v>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>EURUSD=X</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>1.146526</v>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP.AT</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="n"/>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-09-16</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>GBPUSD=X</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>1.338097</v>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>IWDA.L</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>145.889999</v>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>LIGT3.SA</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>SAPR11.SA</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>34.099998</v>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -843,6 +843,57 @@
       </c>
       <c r="O7" s="4" t="n">
         <v>-0.079966</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>92088.67999999999</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>92088.67999999999</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>-0.005812</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>0.00086</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP:ATSE:NO_PRICE</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>0.00011</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>-0.079113</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>-0.07330100000000001</v>
+      </c>
+      <c r="O8" s="4" t="n">
+        <v>-0.079973</v>
       </c>
     </row>
   </sheetData>
@@ -1030,7 +1081,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -1074,11 +1125,11 @@
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="5" t="n">
-        <v>34.099998</v>
+        <v>34.110001</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="K3" s="3" t="n"/>
@@ -1131,11 +1182,11 @@
       </c>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="5" t="n">
-        <v>3.62</v>
+        <v>3.55</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="K4" s="3" t="n"/>
@@ -1881,7 +1932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3106,6 +3157,204 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>BRLUSD=X</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>0.195145</v>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>CHFUSD=X</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>1.213931</v>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>EURUSD=X</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>1.148106</v>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP.AT</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="n"/>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-09-17</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>GBPUSD=X</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>1.335863</v>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>IWDA.L</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>146.220001</v>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>LIGT3.SA</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>SAPR11.SA</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>34.110001</v>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -894,6 +894,57 @@
       </c>
       <c r="O8" s="4" t="n">
         <v>-0.079973</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>92098.77</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>92098.77</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>-0.009415</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>0.000968</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP:ATSE:NO_PRICE</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>0.00011</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>-0.079012</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>-0.06959700000000001</v>
+      </c>
+      <c r="O9" s="4" t="n">
+        <v>-0.07998</v>
       </c>
     </row>
   </sheetData>
@@ -1081,7 +1132,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -1125,11 +1176,11 @@
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="5" t="n">
-        <v>34.110001</v>
+        <v>34.509998</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="K3" s="3" t="n"/>
@@ -1182,11 +1233,11 @@
       </c>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="5" t="n">
-        <v>3.55</v>
+        <v>3.62</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="K4" s="3" t="n"/>
@@ -1932,7 +1983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3355,6 +3406,204 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>BRLUSD=X</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>0.194424</v>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>CHFUSD=X</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>1.216826</v>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>EURUSD=X</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>1.148897</v>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP.AT</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="n"/>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-09-18</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>GBPUSD=X</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>1.339351</v>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>IWDA.L</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>145.690002</v>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>LIGT3.SA</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>SAPR11.SA</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>34.509998</v>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -945,6 +945,57 @@
       </c>
       <c r="O9" s="4" t="n">
         <v>-0.07998</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>92129.05</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>30.28</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>92129.05</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>0.002619</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>0.00129</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP:ATSE:NO_PRICE</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>0.000329</v>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>-0.078709</v>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>-0.081328</v>
+      </c>
+      <c r="O10" s="4" t="n">
+        <v>-0.079999</v>
       </c>
     </row>
   </sheetData>
@@ -1132,7 +1183,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -1176,11 +1227,11 @@
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="5" t="n">
-        <v>34.509998</v>
+        <v>35.349998</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="K3" s="3" t="n"/>
@@ -1233,11 +1284,11 @@
       </c>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="5" t="n">
-        <v>3.62</v>
+        <v>3.59</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="K4" s="3" t="n"/>
@@ -1983,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3604,6 +3655,204 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>BRLUSD=X</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="n">
+        <v>0.195595</v>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>CHFUSD=X</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>1.218621</v>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>EURUSD=X</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="n">
+        <v>1.146657</v>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP.AT</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="n"/>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-09-21</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>GBPUSD=X</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="n">
+        <v>1.337041</v>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>IWDA.L</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="n">
+        <v>147.460007</v>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>LIGT3.SA</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>SAPR11.SA</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>35.349998</v>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -996,6 +996,57 @@
       </c>
       <c r="O10" s="4" t="n">
         <v>-0.079999</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>92139.14999999999</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>92139.14999999999</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>0.006019</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>0.001398</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP:ATSE:NO_PRICE</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>0.00011</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>-0.078609</v>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="4" t="n">
+        <v>-0.08462799999999999</v>
+      </c>
+      <c r="O11" s="4" t="n">
+        <v>-0.08000699999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1183,7 +1234,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -1227,11 +1278,11 @@
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="5" t="n">
-        <v>35.349998</v>
+        <v>34.810001</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="K3" s="3" t="n"/>
@@ -1284,11 +1335,11 @@
       </c>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="5" t="n">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="K4" s="3" t="n"/>
@@ -2034,7 +2085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3853,6 +3904,204 @@
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>BRLUSD=X</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="n">
+        <v>0.19604</v>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>CHFUSD=X</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>1.219988</v>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>EURUSD=X</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="n">
+        <v>1.145082</v>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP.AT</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="n"/>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-09-22</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>GBPUSD=X</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="n">
+        <v>1.334917</v>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>IWDA.L</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="n">
+        <v>147.960007</v>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>LIGT3.SA</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>SAPR11.SA</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="n">
+        <v>34.810001</v>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1047,6 +1047,57 @@
       </c>
       <c r="O11" s="4" t="n">
         <v>-0.08000699999999999</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>92149.25</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>92149.25</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>-0.00044</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>0.001505</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP:ATSE:NO_PRICE</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>0.00011</v>
+      </c>
+      <c r="L12" s="4" t="n">
+        <v>-0.07850699999999999</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="4" t="n">
+        <v>-0.078067</v>
+      </c>
+      <c r="O12" s="4" t="n">
+        <v>-0.080012</v>
       </c>
     </row>
   </sheetData>
@@ -1234,7 +1285,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -1278,11 +1329,11 @@
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="5" t="n">
-        <v>34.810001</v>
+        <v>34.040001</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K3" s="3" t="n"/>
@@ -1335,11 +1386,11 @@
       </c>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="5" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="K4" s="3" t="n"/>
@@ -2085,7 +2136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E81"/>
+  <dimension ref="A1:E89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4102,6 +4153,204 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>BRLUSD=X</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="n">
+        <v>0.193558</v>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>CHFUSD=X</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="n">
+        <v>1.213136</v>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>EURUSD=X</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="n">
+        <v>1.138952</v>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP.AT</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="n"/>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-09-23</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>GBPUSD=X</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="n">
+        <v>1.324661</v>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>IWDA.L</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="n">
+        <v>147.009995</v>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>LIGT3.SA</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>SAPR11.SA</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="n">
+        <v>34.040001</v>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1098,6 +1098,57 @@
       </c>
       <c r="O12" s="4" t="n">
         <v>-0.080012</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>92159.35000000001</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>92159.35000000001</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>-0.007988</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>0.001613</v>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP:ATSE:NO_PRICE</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>0.00011</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>-0.078406</v>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="4" t="n">
+        <v>-0.07041799999999999</v>
+      </c>
+      <c r="O13" s="4" t="n">
+        <v>-0.08001900000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1285,7 +1336,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -1329,11 +1380,11 @@
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="5" t="n">
-        <v>34.040001</v>
+        <v>33.560001</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="K3" s="3" t="n"/>
@@ -1386,11 +1437,11 @@
       </c>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="5" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="K4" s="3" t="n"/>
@@ -2136,7 +2187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E89"/>
+  <dimension ref="A1:E97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4351,6 +4402,204 @@
         </is>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>BRLUSD=X</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="n">
+        <v>0.192626</v>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>CHFUSD=X</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="n">
+        <v>1.209292</v>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>EURUSD=X</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="n">
+        <v>1.138174</v>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP.AT</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="n"/>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-09-24</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>GBPUSD=X</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="n">
+        <v>1.321528</v>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>IWDA.L</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="n">
+        <v>145.899994</v>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>LIGT3.SA</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>SAPR11.SA</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="n">
+        <v>33.560001</v>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1149,6 +1149,57 @@
       </c>
       <c r="O13" s="4" t="n">
         <v>-0.08001900000000001</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>92169.44</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>92169.44</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>-0.00112</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>0.001721</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP:ATSE:NO_PRICE</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>0.000109</v>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>-0.078306</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>-0.077186</v>
+      </c>
+      <c r="O14" s="4" t="n">
+        <v>-0.080027</v>
       </c>
     </row>
   </sheetData>
@@ -1336,7 +1387,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -1380,11 +1431,11 @@
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="5" t="n">
-        <v>33.560001</v>
+        <v>33.349998</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="K3" s="3" t="n"/>
@@ -1437,11 +1488,11 @@
       </c>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="5" t="n">
-        <v>3.45</v>
+        <v>3.49</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="K4" s="3" t="n"/>
@@ -2187,7 +2238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E97"/>
+  <dimension ref="A1:E105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4600,6 +4651,204 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>BRLUSD=X</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="n">
+        <v>0.192805</v>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>CHFUSD=X</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="n">
+        <v>1.207292</v>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>EURUSD=X</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="n">
+        <v>1.139212</v>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP.AT</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="n"/>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-09-25</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>GBPUSD=X</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="n">
+        <v>1.324644</v>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>IWDA.L</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="n">
+        <v>146.910004</v>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>LIGT3.SA</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>SAPR11.SA</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="n">
+        <v>33.349998</v>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1200,6 +1200,57 @@
       </c>
       <c r="O14" s="4" t="n">
         <v>-0.080027</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>92199.75</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>92199.75</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>-0.006084</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>0.002044</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP:ATSE:NO_PRICE</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="n">
+        <v>0.000329</v>
+      </c>
+      <c r="L15" s="4" t="n">
+        <v>-0.078002</v>
+      </c>
+      <c r="M15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="4" t="n">
+        <v>-0.071918</v>
+      </c>
+      <c r="O15" s="4" t="n">
+        <v>-0.08004600000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1387,7 +1438,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -1431,11 +1482,11 @@
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="5" t="n">
-        <v>33.349998</v>
+        <v>33.040001</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="K3" s="3" t="n"/>
@@ -1488,11 +1539,11 @@
       </c>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="5" t="n">
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="K4" s="3" t="n"/>
@@ -2238,7 +2289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E105"/>
+  <dimension ref="A1:E113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4849,6 +4900,204 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>BRLUSD=X</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="n">
+        <v>0.191435</v>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>CHFUSD=X</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="n">
+        <v>1.202776</v>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>EURUSD=X</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="n">
+        <v>1.137398</v>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP.AT</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="n"/>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-09-28</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>GBPUSD=X</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="n">
+        <v>1.325574</v>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>IWDA.L</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="n">
+        <v>146.179993</v>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>LIGT3.SA</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>SAPR11.SA</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="n">
+        <v>33.040001</v>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1251,6 +1251,57 @@
       </c>
       <c r="O15" s="4" t="n">
         <v>-0.08004600000000001</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>92209.85000000001</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>92209.85000000001</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>-0.008192</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>0.002151</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP:ATSE:NO_PRICE</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>0.00011</v>
+      </c>
+      <c r="L16" s="4" t="n">
+        <v>-0.077901</v>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="4" t="n">
+        <v>-0.06970899999999999</v>
+      </c>
+      <c r="O16" s="4" t="n">
+        <v>-0.080052</v>
       </c>
     </row>
   </sheetData>
@@ -1438,7 +1489,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -1482,11 +1533,11 @@
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="5" t="n">
-        <v>33.040001</v>
+        <v>32.939999</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="K3" s="3" t="n"/>
@@ -1539,11 +1590,11 @@
       </c>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="5" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="K4" s="3" t="n"/>
@@ -2289,7 +2340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E113"/>
+  <dimension ref="A1:E121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5098,6 +5149,204 @@
         </is>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>BRLUSD=X</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="n">
+        <v>0.192193</v>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>CHFUSD=X</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="n">
+        <v>1.200538</v>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>EURUSD=X</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="n">
+        <v>1.134687</v>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP.AT</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="n"/>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-09-29</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>GBPUSD=X</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="n">
+        <v>1.322891</v>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>IWDA.L</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="n">
+        <v>145.869995</v>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>LIGT3.SA</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>SAPR11.SA</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="n">
+        <v>32.939999</v>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1302,6 +1302,57 @@
       </c>
       <c r="O16" s="4" t="n">
         <v>-0.080052</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>92219.96000000001</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>92219.96000000001</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>-0.002684</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>0.002259</v>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP:ATSE:NO_PRICE</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>0.00011</v>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>-0.07779999999999999</v>
+      </c>
+      <c r="M17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="4" t="n">
+        <v>-0.075116</v>
+      </c>
+      <c r="O17" s="4" t="n">
+        <v>-0.08005900000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1489,7 +1540,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -1533,11 +1584,11 @@
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="5" t="n">
-        <v>32.939999</v>
+        <v>33.009998</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="K3" s="3" t="n"/>
@@ -1590,11 +1641,11 @@
       </c>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="5" t="n">
-        <v>3.65</v>
+        <v>3.72</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="K4" s="3" t="n"/>
@@ -2340,7 +2391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E121"/>
+  <dimension ref="A1:E129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5347,6 +5398,204 @@
         </is>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>BRLUSD=X</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="n">
+        <v>0.192957</v>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>CHFUSD=X</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="n">
+        <v>1.198538</v>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>EURUSD=X</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="n">
+        <v>1.133273</v>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP.AT</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="n"/>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-09-30</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>GBPUSD=X</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="n">
+        <v>1.32714</v>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>IWDA.L</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="n">
+        <v>146.679993</v>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>LIGT3.SA</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>SAPR11.SA</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="n">
+        <v>33.009998</v>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1353,6 +1353,57 @@
       </c>
       <c r="O17" s="4" t="n">
         <v>-0.08005900000000001</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>92230.06</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>92230.06</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>-0.016419</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>0.002367</v>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP:ATSE:NO_PRICE</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>0.00011</v>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>-0.077699</v>
+      </c>
+      <c r="M18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="4" t="n">
+        <v>-0.06128</v>
+      </c>
+      <c r="O18" s="4" t="n">
+        <v>-0.080066</v>
       </c>
     </row>
   </sheetData>
@@ -1540,7 +1591,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -1584,11 +1635,11 @@
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="5" t="n">
-        <v>33.009998</v>
+        <v>33.59</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="K3" s="3" t="n"/>
@@ -1641,11 +1692,11 @@
       </c>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="5" t="n">
-        <v>3.72</v>
+        <v>3.67</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="K4" s="3" t="n"/>
@@ -2391,7 +2442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E129"/>
+  <dimension ref="A1:E137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5596,6 +5647,204 @@
         </is>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>BRLUSD=X</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="n">
+        <v>0.191479</v>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>CHFUSD=X</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="n">
+        <v>1.204021</v>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>EURUSD=X</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="n">
+        <v>1.124733</v>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP.AT</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="n"/>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-10-01</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>GBPUSD=X</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="n">
+        <v>1.319906</v>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>IWDA.L</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="n">
+        <v>144.660004</v>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>LIGT3.SA</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>SAPR11.SA</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="n">
+        <v>33.59</v>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1404,6 +1404,57 @@
       </c>
       <c r="O18" s="4" t="n">
         <v>-0.080066</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>92240.17</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>92240.17</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>-0.004044</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>0.002474</v>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP:ATSE:NO_PRICE</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>0.00011</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>-0.077598</v>
+      </c>
+      <c r="M19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="4" t="n">
+        <v>-0.07355399999999999</v>
+      </c>
+      <c r="O19" s="4" t="n">
+        <v>-0.080072</v>
       </c>
     </row>
   </sheetData>
@@ -1591,7 +1642,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -1635,11 +1686,11 @@
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="5" t="n">
-        <v>33.59</v>
+        <v>35.209999</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="K3" s="3" t="n"/>
@@ -1692,11 +1743,11 @@
       </c>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="5" t="n">
-        <v>3.67</v>
+        <v>3.77</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="K4" s="3" t="n"/>
@@ -2442,7 +2493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E137"/>
+  <dimension ref="A1:E145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5845,6 +5896,204 @@
         </is>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>BRLUSD=X</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="n">
+        <v>0.191674</v>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>CHFUSD=X</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="n">
+        <v>1.20703</v>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>EURUSD=X</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="n">
+        <v>1.125746</v>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP.AT</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="n"/>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-10-02</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>GBPUSD=X</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="n">
+        <v>1.324047</v>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>IWDA.L</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="n">
+        <v>146.479996</v>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>LIGT3.SA</t>
+        </is>
+      </c>
+      <c r="C144" s="5" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>SAPR11.SA</t>
+        </is>
+      </c>
+      <c r="C145" s="5" t="n">
+        <v>35.209999</v>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1455,6 +1455,57 @@
       </c>
       <c r="O19" s="4" t="n">
         <v>-0.080072</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>92270.5</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>30.33</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>92270.5</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>-3.2e-05</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>0.002798</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP:ATSE:NO_PRICE</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="n">
+        <v>0.000329</v>
+      </c>
+      <c r="L20" s="4" t="n">
+        <v>-0.077295</v>
+      </c>
+      <c r="M20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="4" t="n">
+        <v>-0.077263</v>
+      </c>
+      <c r="O20" s="4" t="n">
+        <v>-0.080093</v>
       </c>
     </row>
   </sheetData>
@@ -1642,7 +1693,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -1686,11 +1737,11 @@
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="5" t="n">
-        <v>35.209999</v>
+        <v>37.810001</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="K3" s="3" t="n"/>
@@ -1743,11 +1794,11 @@
       </c>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="5" t="n">
-        <v>3.77</v>
+        <v>3.96</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="K4" s="3" t="n"/>
@@ -2493,7 +2544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E145"/>
+  <dimension ref="A1:E153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6094,6 +6145,204 @@
         </is>
       </c>
     </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>BRLUSD=X</t>
+        </is>
+      </c>
+      <c r="C146" s="5" t="n">
+        <v>0.200212</v>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>CHFUSD=X</t>
+        </is>
+      </c>
+      <c r="C147" s="5" t="n">
+        <v>1.203949</v>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>EURUSD=X</t>
+        </is>
+      </c>
+      <c r="C148" s="5" t="n">
+        <v>1.122586</v>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP.AT</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="n"/>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-10-05</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>GBPUSD=X</t>
+        </is>
+      </c>
+      <c r="C150" s="5" t="n">
+        <v>1.321825</v>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>IWDA.L</t>
+        </is>
+      </c>
+      <c r="C151" s="5" t="n">
+        <v>147.070007</v>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>LIGT3.SA</t>
+        </is>
+      </c>
+      <c r="C152" s="5" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>SAPR11.SA</t>
+        </is>
+      </c>
+      <c r="C153" s="5" t="n">
+        <v>37.810001</v>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O20"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1506,6 +1506,57 @@
       </c>
       <c r="O20" s="4" t="n">
         <v>-0.080093</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>92280.61</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>92280.61</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>0.010302</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>0.002905</v>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP:ATSE:NO_PRICE</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>0.00011</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>-0.077194</v>
+      </c>
+      <c r="M21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="4" t="n">
+        <v>-0.087496</v>
+      </c>
+      <c r="O21" s="4" t="n">
+        <v>-0.080099</v>
       </c>
     </row>
   </sheetData>
@@ -1693,7 +1744,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -1737,11 +1788,11 @@
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="5" t="n">
-        <v>37.810001</v>
+        <v>38.52</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="K3" s="3" t="n"/>
@@ -1794,11 +1845,11 @@
       </c>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="5" t="n">
-        <v>3.96</v>
+        <v>3.91</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="K4" s="3" t="n"/>
@@ -2544,7 +2595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E153"/>
+  <dimension ref="A1:E161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6343,6 +6394,204 @@
         </is>
       </c>
     </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>BRLUSD=X</t>
+        </is>
+      </c>
+      <c r="C154" s="5" t="n">
+        <v>0.200662</v>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>CHFUSD=X</t>
+        </is>
+      </c>
+      <c r="C155" s="5" t="n">
+        <v>1.203138</v>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>EURUSD=X</t>
+        </is>
+      </c>
+      <c r="C156" s="5" t="n">
+        <v>1.126126</v>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP.AT</t>
+        </is>
+      </c>
+      <c r="C157" s="5" t="n"/>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-10-06</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>GBPUSD=X</t>
+        </is>
+      </c>
+      <c r="C158" s="5" t="n">
+        <v>1.327492</v>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>IWDA.L</t>
+        </is>
+      </c>
+      <c r="C159" s="5" t="n">
+        <v>148.589996</v>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>LIGT3.SA</t>
+        </is>
+      </c>
+      <c r="C160" s="5" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>SAPR11.SA</t>
+        </is>
+      </c>
+      <c r="C161" s="5" t="n">
+        <v>38.52</v>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1557,6 +1557,57 @@
       </c>
       <c r="O21" s="4" t="n">
         <v>-0.080099</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>92290.72</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>92290.72</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>-0.000168</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>0.003013</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP:ATSE:NO_PRICE</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="n">
+        <v>0.00011</v>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>-0.07709299999999999</v>
+      </c>
+      <c r="M22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="4" t="n">
+        <v>-0.07692499999999999</v>
+      </c>
+      <c r="O22" s="4" t="n">
+        <v>-0.080106</v>
       </c>
     </row>
   </sheetData>
@@ -1744,7 +1795,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -1788,11 +1839,11 @@
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="5" t="n">
-        <v>38.52</v>
+        <v>41.970001</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K3" s="3" t="n"/>
@@ -1845,11 +1896,11 @@
       </c>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="5" t="n">
-        <v>3.91</v>
+        <v>3.94</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="K4" s="3" t="n"/>
@@ -2595,7 +2646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E161"/>
+  <dimension ref="A1:E169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6592,6 +6643,204 @@
         </is>
       </c>
     </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>BRLUSD=X</t>
+        </is>
+      </c>
+      <c r="C162" s="5" t="n">
+        <v>0.199132</v>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>CHFUSD=X</t>
+        </is>
+      </c>
+      <c r="C163" s="5" t="n">
+        <v>1.20074</v>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>EURUSD=X</t>
+        </is>
+      </c>
+      <c r="C164" s="5" t="n">
+        <v>1.119695</v>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP.AT</t>
+        </is>
+      </c>
+      <c r="C165" s="5" t="n"/>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-10-07</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>GBPUSD=X</t>
+        </is>
+      </c>
+      <c r="C166" s="5" t="n">
+        <v>1.32165</v>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>IWDA.L</t>
+        </is>
+      </c>
+      <c r="C167" s="5" t="n">
+        <v>147.050003</v>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>LIGT3.SA</t>
+        </is>
+      </c>
+      <c r="C168" s="5" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>SAPR11.SA</t>
+        </is>
+      </c>
+      <c r="C169" s="5" t="n">
+        <v>41.970001</v>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1608,6 +1608,57 @@
       </c>
       <c r="O22" s="4" t="n">
         <v>-0.080106</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>92300.83</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>92300.83</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>-0.002752</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>0.003121</v>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP:ATSE:NO_PRICE</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="n">
+        <v>0.00011</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>-0.076992</v>
+      </c>
+      <c r="M23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="4" t="n">
+        <v>-0.07424</v>
+      </c>
+      <c r="O23" s="4" t="n">
+        <v>-0.080113</v>
       </c>
     </row>
   </sheetData>
@@ -1795,7 +1846,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -1839,11 +1890,11 @@
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="5" t="n">
-        <v>41.970001</v>
+        <v>43.049999</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="K3" s="3" t="n"/>
@@ -1896,11 +1947,11 @@
       </c>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="5" t="n">
-        <v>3.94</v>
+        <v>3.85</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="K4" s="3" t="n"/>
@@ -2646,7 +2697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E169"/>
+  <dimension ref="A1:E177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6841,6 +6892,204 @@
         </is>
       </c>
     </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>BRLUSD=X</t>
+        </is>
+      </c>
+      <c r="C170" s="5" t="n">
+        <v>0.199334</v>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>CHFUSD=X</t>
+        </is>
+      </c>
+      <c r="C171" s="5" t="n">
+        <v>1.203427</v>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>EURUSD=X</t>
+        </is>
+      </c>
+      <c r="C172" s="5" t="n">
+        <v>1.121705</v>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP.AT</t>
+        </is>
+      </c>
+      <c r="C173" s="5" t="n"/>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-10-08</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>GBPUSD=X</t>
+        </is>
+      </c>
+      <c r="C174" s="5" t="n">
+        <v>1.323241</v>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>IWDA.L</t>
+        </is>
+      </c>
+      <c r="C175" s="5" t="n">
+        <v>146.669998</v>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>LIGT3.SA</t>
+        </is>
+      </c>
+      <c r="C176" s="5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>SAPR11.SA</t>
+        </is>
+      </c>
+      <c r="C177" s="5" t="n">
+        <v>43.049999</v>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1659,6 +1659,57 @@
       </c>
       <c r="O23" s="4" t="n">
         <v>-0.080113</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>92310.95</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>92310.95</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>0.002279</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>0.003229</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP:ATSE:NO_PRICE</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="n">
+        <v>0.00011</v>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>-0.076891</v>
+      </c>
+      <c r="M24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="4" t="n">
+        <v>-0.07917</v>
+      </c>
+      <c r="O24" s="4" t="n">
+        <v>-0.08012</v>
       </c>
     </row>
   </sheetData>
@@ -1846,7 +1897,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -1890,11 +1941,11 @@
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="5" t="n">
-        <v>43.049999</v>
+        <v>45.07</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="K3" s="3" t="n"/>
@@ -1947,11 +1998,11 @@
       </c>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="5" t="n">
-        <v>3.85</v>
+        <v>3.94</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="K4" s="3" t="n"/>
@@ -2697,7 +2748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E177"/>
+  <dimension ref="A1:E185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7090,6 +7141,204 @@
         </is>
       </c>
     </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>BRLUSD=X</t>
+        </is>
+      </c>
+      <c r="C178" s="5" t="n">
+        <v>0.200349</v>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>CHFUSD=X</t>
+        </is>
+      </c>
+      <c r="C179" s="5" t="n">
+        <v>1.204819</v>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>EURUSD=X</t>
+        </is>
+      </c>
+      <c r="C180" s="5" t="n">
+        <v>1.120574</v>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP.AT</t>
+        </is>
+      </c>
+      <c r="C181" s="5" t="n"/>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-10-09</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>GBPUSD=X</t>
+        </is>
+      </c>
+      <c r="C182" s="5" t="n">
+        <v>1.323311</v>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>IWDA.L</t>
+        </is>
+      </c>
+      <c r="C183" s="5" t="n">
+        <v>147.410004</v>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>LIGT3.SA</t>
+        </is>
+      </c>
+      <c r="C184" s="5" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>SAPR11.SA</t>
+        </is>
+      </c>
+      <c r="C185" s="5" t="n">
+        <v>45.07</v>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1710,6 +1710,57 @@
       </c>
       <c r="O24" s="4" t="n">
         <v>-0.08012</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>92351.41</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>40.47</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>92351.41</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>0.002279</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>0.00366</v>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP:ATSE:NO_PRICE</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="n">
+        <v>0.000438</v>
+      </c>
+      <c r="L25" s="4" t="n">
+        <v>-0.076486</v>
+      </c>
+      <c r="M25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="4" t="n">
+        <v>-0.078765</v>
+      </c>
+      <c r="O25" s="4" t="n">
+        <v>-0.080146</v>
       </c>
     </row>
   </sheetData>
@@ -1897,7 +1948,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>-9</v>
+        <v>-13</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -2748,7 +2799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E185"/>
+  <dimension ref="A1:E193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7339,6 +7390,198 @@
         </is>
       </c>
     </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>BRLUSD=X</t>
+        </is>
+      </c>
+      <c r="C186" s="5" t="n">
+        <v>0.20055</v>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>CHFUSD=X</t>
+        </is>
+      </c>
+      <c r="C187" s="5" t="n">
+        <v>1.200509</v>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>EURUSD=X</t>
+        </is>
+      </c>
+      <c r="C188" s="5" t="n">
+        <v>1.117693</v>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP.AT</t>
+        </is>
+      </c>
+      <c r="C189" s="5" t="n"/>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-10-13</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>GBPUSD=X</t>
+        </is>
+      </c>
+      <c r="C190" s="5" t="n">
+        <v>1.321929</v>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>IWDA.L</t>
+        </is>
+      </c>
+      <c r="C191" s="5" t="n"/>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-10-13</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>LIGT3.SA</t>
+        </is>
+      </c>
+      <c r="C192" s="5" t="n"/>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-10-13</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>SAPR11.SA</t>
+        </is>
+      </c>
+      <c r="C193" s="5" t="n"/>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-10-13</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1761,6 +1761,57 @@
       </c>
       <c r="O25" s="4" t="n">
         <v>-0.080146</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>92361.53999999999</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>92361.53999999999</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>0.002279</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>0.003768</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP:ATSE:NO_PRICE</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="n">
+        <v>0.00011</v>
+      </c>
+      <c r="L26" s="4" t="n">
+        <v>-0.07638499999999999</v>
+      </c>
+      <c r="M26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="4" t="n">
+        <v>-0.078664</v>
+      </c>
+      <c r="O26" s="4" t="n">
+        <v>-0.080153</v>
       </c>
     </row>
   </sheetData>
@@ -1948,7 +1999,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -2799,7 +2850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E193"/>
+  <dimension ref="A1:E201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7582,6 +7633,196 @@
         </is>
       </c>
     </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>BRLUSD=X</t>
+        </is>
+      </c>
+      <c r="C194" s="5" t="n"/>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-10-14</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>CHFUSD=X</t>
+        </is>
+      </c>
+      <c r="C195" s="5" t="n">
+        <v>1.200999</v>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>EURUSD=X</t>
+        </is>
+      </c>
+      <c r="C196" s="5" t="n">
+        <v>1.120448</v>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP.AT</t>
+        </is>
+      </c>
+      <c r="C197" s="5" t="n"/>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-10-14</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>GBPUSD=X</t>
+        </is>
+      </c>
+      <c r="C198" s="5" t="n">
+        <v>1.325891</v>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>IWDA.L</t>
+        </is>
+      </c>
+      <c r="C199" s="5" t="n"/>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-10-14</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>LIGT3.SA</t>
+        </is>
+      </c>
+      <c r="C200" s="5" t="n"/>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-10-14</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>SAPR11.SA</t>
+        </is>
+      </c>
+      <c r="C201" s="5" t="n"/>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-10-14</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:O27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1812,6 +1812,57 @@
       </c>
       <c r="O26" s="4" t="n">
         <v>-0.080153</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>92371.66</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>92371.66</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>0.002279</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>0.003876</v>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP:ATSE:NO_PRICE</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="n">
+        <v>0.00011</v>
+      </c>
+      <c r="L27" s="4" t="n">
+        <v>-0.076283</v>
+      </c>
+      <c r="M27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="4" t="n">
+        <v>-0.07856200000000001</v>
+      </c>
+      <c r="O27" s="4" t="n">
+        <v>-0.08015899999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1999,7 +2050,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -2850,7 +2901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E201"/>
+  <dimension ref="A1:E209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7823,6 +7874,196 @@
         </is>
       </c>
     </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>BRLUSD=X</t>
+        </is>
+      </c>
+      <c r="C202" s="5" t="n"/>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-10-15</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>CHFUSD=X</t>
+        </is>
+      </c>
+      <c r="C203" s="5" t="n">
+        <v>1.202328</v>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>EURUSD=X</t>
+        </is>
+      </c>
+      <c r="C204" s="5" t="n">
+        <v>1.119946</v>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP.AT</t>
+        </is>
+      </c>
+      <c r="C205" s="5" t="n"/>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-10-15</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>GBPUSD=X</t>
+        </is>
+      </c>
+      <c r="C206" s="5" t="n">
+        <v>1.323399</v>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>IWDA.L</t>
+        </is>
+      </c>
+      <c r="C207" s="5" t="n"/>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-10-15</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>LIGT3.SA</t>
+        </is>
+      </c>
+      <c r="C208" s="5" t="n"/>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-10-15</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>SAPR11.SA</t>
+        </is>
+      </c>
+      <c r="C209" s="5" t="n"/>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-10-15</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -2094,11 +2094,11 @@
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="5" t="n">
-        <v>45.07</v>
+        <v>39.419998</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="K3" s="3" t="n"/>
@@ -2151,11 +2151,11 @@
       </c>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="5" t="n">
-        <v>3.94</v>
+        <v>3.84</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="K4" s="3" t="n"/>
@@ -7885,15 +7885,17 @@
           <t>BRLUSD=X</t>
         </is>
       </c>
-      <c r="C202" s="5" t="n"/>
+      <c r="C202" s="5" t="n">
+        <v>0.198432</v>
+      </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-10-15</t>
+          <t>yfinance</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -7909,7 +7911,7 @@
         </is>
       </c>
       <c r="C203" s="5" t="n">
-        <v>1.202328</v>
+        <v>1.202501</v>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
@@ -7934,7 +7936,7 @@
         </is>
       </c>
       <c r="C204" s="5" t="n">
-        <v>1.119946</v>
+        <v>1.119507</v>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
@@ -7982,7 +7984,7 @@
         </is>
       </c>
       <c r="C206" s="5" t="n">
-        <v>1.323399</v>
+        <v>1.323014</v>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
@@ -8029,15 +8031,17 @@
           <t>LIGT3.SA</t>
         </is>
       </c>
-      <c r="C208" s="5" t="n"/>
+      <c r="C208" s="5" t="n">
+        <v>3.84</v>
+      </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-10-15</t>
+          <t>yfinance</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -8052,15 +8056,17 @@
           <t>SAPR11.SA</t>
         </is>
       </c>
-      <c r="C209" s="5" t="n"/>
+      <c r="C209" s="5" t="n">
+        <v>39.419998</v>
+      </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-10-15</t>
+          <t>yfinance</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>ok</t>
         </is>
       </c>
     </row>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O27"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1863,6 +1863,57 @@
       </c>
       <c r="O27" s="4" t="n">
         <v>-0.08015899999999999</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>92381.78</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>92381.78</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>0.002279</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>0.003984</v>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP:ATSE:NO_PRICE</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="n">
+        <v>0.00011</v>
+      </c>
+      <c r="L28" s="4" t="n">
+        <v>-0.076182</v>
+      </c>
+      <c r="M28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="4" t="n">
+        <v>-0.078461</v>
+      </c>
+      <c r="O28" s="4" t="n">
+        <v>-0.080166</v>
       </c>
     </row>
   </sheetData>
@@ -2050,7 +2101,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -2094,11 +2145,11 @@
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="5" t="n">
-        <v>39.419998</v>
+        <v>40</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K3" s="3" t="n"/>
@@ -2151,11 +2202,11 @@
       </c>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="5" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K4" s="3" t="n"/>
@@ -2901,7 +2952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E209"/>
+  <dimension ref="A1:E217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8070,6 +8121,202 @@
         </is>
       </c>
     </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>BRLUSD=X</t>
+        </is>
+      </c>
+      <c r="C210" s="5" t="n">
+        <v>0.197266</v>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>CHFUSD=X</t>
+        </is>
+      </c>
+      <c r="C211" s="5" t="n">
+        <v>1.214167</v>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>EURUSD=X</t>
+        </is>
+      </c>
+      <c r="C212" s="5" t="n">
+        <v>1.124354</v>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP.AT</t>
+        </is>
+      </c>
+      <c r="C213" s="5" t="n"/>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-10-16</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>GBPUSD=X</t>
+        </is>
+      </c>
+      <c r="C214" s="5" t="n">
+        <v>1.327316</v>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>IWDA.L</t>
+        </is>
+      </c>
+      <c r="C215" s="5" t="n"/>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-10-16</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>LIGT3.SA</t>
+        </is>
+      </c>
+      <c r="C216" s="5" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>SAPR11.SA</t>
+        </is>
+      </c>
+      <c r="C217" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1914,6 +1914,57 @@
       </c>
       <c r="O28" s="4" t="n">
         <v>-0.080166</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>92422.28</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>92422.28</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>0.002279</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>0.004415</v>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP:ATSE:NO_PRICE</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="n">
+        <v>0.000438</v>
+      </c>
+      <c r="L29" s="4" t="n">
+        <v>-0.075777</v>
+      </c>
+      <c r="M29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="4" t="n">
+        <v>-0.078056</v>
+      </c>
+      <c r="O29" s="4" t="n">
+        <v>-0.080192</v>
       </c>
     </row>
   </sheetData>
@@ -2101,7 +2152,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>-16</v>
+        <v>-20</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -2952,7 +3003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E217"/>
+  <dimension ref="A1:E225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8317,6 +8368,196 @@
         </is>
       </c>
     </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>BRLUSD=X</t>
+        </is>
+      </c>
+      <c r="C218" s="5" t="n"/>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-10-20</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>CHFUSD=X</t>
+        </is>
+      </c>
+      <c r="C219" s="5" t="n">
+        <v>1.210698</v>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>EURUSD=X</t>
+        </is>
+      </c>
+      <c r="C220" s="5" t="n">
+        <v>1.122083</v>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP.AT</t>
+        </is>
+      </c>
+      <c r="C221" s="5" t="n"/>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-10-20</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>GBPUSD=X</t>
+        </is>
+      </c>
+      <c r="C222" s="5" t="n">
+        <v>1.33154</v>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>IWDA.L</t>
+        </is>
+      </c>
+      <c r="C223" s="5" t="n"/>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-10-20</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>LIGT3.SA</t>
+        </is>
+      </c>
+      <c r="C224" s="5" t="n"/>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-10-20</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>SAPR11.SA</t>
+        </is>
+      </c>
+      <c r="C225" s="5" t="n"/>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-10-20</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O29"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1965,6 +1965,57 @@
       </c>
       <c r="O29" s="4" t="n">
         <v>-0.080192</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>92432.39999999999</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>10.13</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>92432.39999999999</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>0.002279</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>0.004523</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP:ATSE:NO_PRICE</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="n">
+        <v>0.000109</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>-0.07567599999999999</v>
+      </c>
+      <c r="M30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="4" t="n">
+        <v>-0.077955</v>
+      </c>
+      <c r="O30" s="4" t="n">
+        <v>-0.08019900000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2152,7 +2203,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -3003,7 +3054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E225"/>
+  <dimension ref="A1:E233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8558,6 +8609,196 @@
         </is>
       </c>
     </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>BRLUSD=X</t>
+        </is>
+      </c>
+      <c r="C226" s="5" t="n"/>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-10-21</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>CHFUSD=X</t>
+        </is>
+      </c>
+      <c r="C227" s="5" t="n">
+        <v>1.211284</v>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>EURUSD=X</t>
+        </is>
+      </c>
+      <c r="C228" s="5" t="n">
+        <v>1.122965</v>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP.AT</t>
+        </is>
+      </c>
+      <c r="C229" s="5" t="n"/>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-10-21</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>GBPUSD=X</t>
+        </is>
+      </c>
+      <c r="C230" s="5" t="n">
+        <v>1.337453</v>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>IWDA.L</t>
+        </is>
+      </c>
+      <c r="C231" s="5" t="n"/>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-10-21</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>LIGT3.SA</t>
+        </is>
+      </c>
+      <c r="C232" s="5" t="n"/>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-10-21</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>SAPR11.SA</t>
+        </is>
+      </c>
+      <c r="C233" s="5" t="n"/>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>yfinance-no-close-on-2026-10-21</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -549,7 +549,7 @@
         <v>92007.99000000001</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0</v>
+        <v>7960.17</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>0</v>
@@ -558,7 +558,7 @@
         <v>-7992.01</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>92007.99000000001</v>
+        <v>99968.16</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>1</v>
@@ -569,25 +569,21 @@
       <c r="I2" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>EYDAP:ATSE:NO_PRICE</t>
-        </is>
-      </c>
+      <c r="J2" s="2" t="n"/>
       <c r="K2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>-0.07992</v>
+        <v>-0.000318</v>
       </c>
       <c r="M2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>-0.07642</v>
+        <v>0.003182</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>-0.07992</v>
+        <v>-0.000318</v>
       </c>
     </row>
     <row r="3">
@@ -600,7 +596,7 @@
         <v>92018.07000000001</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0</v>
+        <v>7942.61</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>10.08</v>
@@ -609,7 +605,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>92018.07000000001</v>
+        <v>99960.67999999999</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>1</v>
@@ -620,25 +616,21 @@
       <c r="I3" s="4" t="n">
         <v>0.000107</v>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>EYDAP:ATSE:NO_PRICE</t>
-        </is>
-      </c>
+      <c r="J3" s="2" t="n"/>
       <c r="K3" s="4" t="n">
-        <v>0.00011</v>
+        <v>-7.499999999999999e-05</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>-0.079819</v>
+        <v>-0.000393</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>0</v>
+        <v>-7.499999999999999e-05</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>-0.071356</v>
+        <v>0.008070000000000001</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>-0.079926</v>
+        <v>-0.0005</v>
       </c>
     </row>
     <row r="4">
@@ -651,7 +643,7 @@
         <v>92028.16</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0</v>
+        <v>7922.03</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>10.08</v>
@@ -660,7 +652,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>92028.16</v>
+        <v>99950.19</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>1</v>
@@ -671,25 +663,21 @@
       <c r="I4" s="4" t="n">
         <v>0.000215</v>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>EYDAP:ATSE:NO_PRICE</t>
-        </is>
-      </c>
+      <c r="J4" s="2" t="n"/>
       <c r="K4" s="4" t="n">
-        <v>0.00011</v>
+        <v>-0.000105</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>-0.079718</v>
+        <v>-0.000498</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0</v>
+        <v>-0.00018</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>-0.07893799999999999</v>
+        <v>0.000282</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>-0.079933</v>
+        <v>-0.000713</v>
       </c>
     </row>
     <row r="5">
@@ -702,7 +690,7 @@
         <v>92058.41</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0</v>
+        <v>7612.97</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>30.26</v>
@@ -711,7 +699,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>92058.41</v>
+        <v>99671.38</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>1</v>
@@ -722,25 +710,21 @@
       <c r="I5" s="4" t="n">
         <v>0.000537</v>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>EYDAP:ATSE:NO_PRICE</t>
-        </is>
-      </c>
+      <c r="J5" s="2" t="n"/>
       <c r="K5" s="4" t="n">
-        <v>0.000329</v>
+        <v>-0.002789</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>-0.079416</v>
+        <v>-0.003286</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>0</v>
+        <v>-0.002969</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>-0.071837</v>
+        <v>0.004293</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>-0.079953</v>
+        <v>-0.003823</v>
       </c>
     </row>
     <row r="6">
@@ -753,7 +737,7 @@
         <v>92068.5</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0</v>
+        <v>7748.64</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>10.09</v>
@@ -762,7 +746,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>92068.5</v>
+        <v>99817.14</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>1</v>
@@ -773,25 +757,21 @@
       <c r="I6" s="4" t="n">
         <v>0.000645</v>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>EYDAP:ATSE:NO_PRICE</t>
-        </is>
-      </c>
+      <c r="J6" s="2" t="n"/>
       <c r="K6" s="4" t="n">
-        <v>0.00011</v>
+        <v>0.001462</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.079315</v>
+        <v>-0.001829</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0</v>
+        <v>-0.001511</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.066636</v>
+        <v>0.01085</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.07996</v>
+        <v>-0.002474</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +784,7 @@
         <v>92078.59</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0</v>
+        <v>8011.14</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>10.09</v>
@@ -813,7 +793,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>92078.59</v>
+        <v>100089.74</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>1</v>
@@ -824,25 +804,21 @@
       <c r="I7" s="4" t="n">
         <v>0.000752</v>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>EYDAP:ATSE:NO_PRICE</t>
-        </is>
-      </c>
+      <c r="J7" s="2" t="n"/>
       <c r="K7" s="4" t="n">
-        <v>0.00011</v>
+        <v>0.002731</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.07921400000000001</v>
+        <v>0.000897</v>
       </c>
       <c r="M7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.071159</v>
+        <v>0.008952</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.079966</v>
+        <v>0.000145</v>
       </c>
     </row>
     <row r="8">
@@ -855,7 +831,7 @@
         <v>92088.67999999999</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0</v>
+        <v>8074.45</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>10.09</v>
@@ -864,7 +840,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>92088.67999999999</v>
+        <v>100163.13</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>1</v>
@@ -875,25 +851,21 @@
       <c r="I8" s="4" t="n">
         <v>0.00086</v>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>EYDAP:ATSE:NO_PRICE</t>
-        </is>
-      </c>
+      <c r="J8" s="2" t="n"/>
       <c r="K8" s="4" t="n">
-        <v>0.00011</v>
+        <v>0.000733</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.079113</v>
+        <v>0.001631</v>
       </c>
       <c r="M8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.07330100000000001</v>
+        <v>0.007443</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.079973</v>
+        <v>0.000771</v>
       </c>
     </row>
     <row r="9">
@@ -906,7 +878,7 @@
         <v>92098.77</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>8158.46</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>10.09</v>
@@ -915,7 +887,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>92098.77</v>
+        <v>100257.23</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>1</v>
@@ -926,25 +898,21 @@
       <c r="I9" s="4" t="n">
         <v>0.000968</v>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>EYDAP:ATSE:NO_PRICE</t>
-        </is>
-      </c>
+      <c r="J9" s="2" t="n"/>
       <c r="K9" s="4" t="n">
-        <v>0.00011</v>
+        <v>0.0009389999999999999</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.079012</v>
+        <v>0.002572</v>
       </c>
       <c r="M9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.06959700000000001</v>
+        <v>0.011987</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.07998</v>
+        <v>0.001604</v>
       </c>
     </row>
     <row r="10">
@@ -957,7 +925,7 @@
         <v>92129.05</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>7959.86</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>30.28</v>
@@ -966,7 +934,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>92129.05</v>
+        <v>100088.92</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>1</v>
@@ -977,25 +945,21 @@
       <c r="I10" s="4" t="n">
         <v>0.00129</v>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>EYDAP:ATSE:NO_PRICE</t>
-        </is>
-      </c>
+      <c r="J10" s="2" t="n"/>
       <c r="K10" s="4" t="n">
-        <v>0.000329</v>
+        <v>-0.001679</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.078709</v>
+        <v>0.000889</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0</v>
+        <v>-0.001679</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.081328</v>
+        <v>-0.00173</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.079999</v>
+        <v>-0.000401</v>
       </c>
     </row>
     <row r="11">
@@ -1008,7 +972,7 @@
         <v>92139.14999999999</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0</v>
+        <v>8131.36</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>10.1</v>
@@ -1017,7 +981,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>92139.14999999999</v>
+        <v>100270.51</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>1</v>
@@ -1028,25 +992,21 @@
       <c r="I11" s="4" t="n">
         <v>0.001398</v>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>EYDAP:ATSE:NO_PRICE</t>
-        </is>
-      </c>
+      <c r="J11" s="2" t="n"/>
       <c r="K11" s="4" t="n">
-        <v>0.00011</v>
+        <v>0.001814</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.078609</v>
+        <v>0.002705</v>
       </c>
       <c r="M11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.08462799999999999</v>
+        <v>-0.003314</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.08000699999999999</v>
+        <v>0.001307</v>
       </c>
     </row>
     <row r="12">
@@ -1059,7 +1019,7 @@
         <v>92149.25</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>7932.3</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>10.1</v>
@@ -1068,7 +1028,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>92149.25</v>
+        <v>100081.55</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>1</v>
@@ -1079,25 +1039,21 @@
       <c r="I12" s="4" t="n">
         <v>0.001505</v>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>EYDAP:ATSE:NO_PRICE</t>
-        </is>
-      </c>
+      <c r="J12" s="2" t="n"/>
       <c r="K12" s="4" t="n">
-        <v>0.00011</v>
+        <v>-0.001885</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.07850699999999999</v>
+        <v>0.000816</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0</v>
+        <v>-0.001885</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.078067</v>
+        <v>0.001256</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.080012</v>
+        <v>-0.0006890000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1110,7 +1066,7 @@
         <v>92159.35000000001</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>7849.17</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>10.1</v>
@@ -1119,7 +1075,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>92159.35000000001</v>
+        <v>100008.51</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>1</v>
@@ -1130,25 +1086,21 @@
       <c r="I13" s="4" t="n">
         <v>0.001613</v>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>EYDAP:ATSE:NO_PRICE</t>
-        </is>
-      </c>
+      <c r="J13" s="2" t="n"/>
       <c r="K13" s="4" t="n">
-        <v>0.00011</v>
+        <v>-0.00073</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.078406</v>
+        <v>8.500000000000001e-05</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0</v>
+        <v>-0.002613</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.07041799999999999</v>
+        <v>0.008073</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.08001900000000001</v>
+        <v>-0.001528</v>
       </c>
     </row>
     <row r="14">
@@ -1161,7 +1113,7 @@
         <v>92169.44</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0</v>
+        <v>7882.25</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>10.1</v>
@@ -1170,7 +1122,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>92169.44</v>
+        <v>100051.7</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>1</v>
@@ -1181,25 +1133,21 @@
       <c r="I14" s="4" t="n">
         <v>0.001721</v>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>EYDAP:ATSE:NO_PRICE</t>
-        </is>
-      </c>
+      <c r="J14" s="2" t="n"/>
       <c r="K14" s="4" t="n">
-        <v>0.000109</v>
+        <v>0.000432</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.078306</v>
+        <v>0.000517</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0</v>
+        <v>-0.002182</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.077186</v>
+        <v>0.001637</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.080027</v>
+        <v>-0.001204</v>
       </c>
     </row>
     <row r="15">
@@ -1212,7 +1160,7 @@
         <v>92199.75</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0</v>
+        <v>8050.91</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>30.3</v>
@@ -1221,7 +1169,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>92199.75</v>
+        <v>100250.66</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>1</v>
@@ -1232,25 +1180,21 @@
       <c r="I15" s="4" t="n">
         <v>0.002044</v>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>EYDAP:ATSE:NO_PRICE</t>
-        </is>
-      </c>
+      <c r="J15" s="2" t="n"/>
       <c r="K15" s="4" t="n">
-        <v>0.000329</v>
+        <v>0.001989</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.078002</v>
+        <v>0.002507</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0</v>
+        <v>-0.000198</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.071918</v>
+        <v>0.008591</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.08004600000000001</v>
+        <v>0.000463</v>
       </c>
     </row>
     <row r="16">
@@ -1263,7 +1207,7 @@
         <v>92209.85000000001</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0</v>
+        <v>7967.16</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>10.1</v>
@@ -1272,7 +1216,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>92209.85000000001</v>
+        <v>100177.01</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>1</v>
@@ -1283,25 +1227,21 @@
       <c r="I16" s="4" t="n">
         <v>0.002151</v>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>EYDAP:ATSE:NO_PRICE</t>
-        </is>
-      </c>
+      <c r="J16" s="2" t="n"/>
       <c r="K16" s="4" t="n">
-        <v>0.00011</v>
+        <v>-0.000735</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.077901</v>
+        <v>0.00177</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0</v>
+        <v>-0.000932</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.06970899999999999</v>
+        <v>0.009962</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.080052</v>
+        <v>-0.000381</v>
       </c>
     </row>
     <row r="17">
@@ -1314,7 +1254,7 @@
         <v>92219.96000000001</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
+        <v>7944.33</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>10.11</v>
@@ -1323,7 +1263,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>92219.96000000001</v>
+        <v>100164.29</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>1</v>
@@ -1334,25 +1274,21 @@
       <c r="I17" s="4" t="n">
         <v>0.002259</v>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>EYDAP:ATSE:NO_PRICE</t>
-        </is>
-      </c>
+      <c r="J17" s="2" t="n"/>
       <c r="K17" s="4" t="n">
-        <v>0.00011</v>
+        <v>-0.000127</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.07779999999999999</v>
+        <v>0.001643</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0</v>
+        <v>-0.001059</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.075116</v>
+        <v>0.004327</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.08005900000000001</v>
+        <v>-0.000616</v>
       </c>
     </row>
     <row r="18">
@@ -1365,7 +1301,7 @@
         <v>92230.06</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0</v>
+        <v>7948.47</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>10.11</v>
@@ -1374,7 +1310,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>92230.06</v>
+        <v>100178.53</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>1</v>
@@ -1385,25 +1321,21 @@
       <c r="I18" s="4" t="n">
         <v>0.002367</v>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>EYDAP:ATSE:NO_PRICE</t>
-        </is>
-      </c>
+      <c r="J18" s="2" t="n"/>
       <c r="K18" s="4" t="n">
-        <v>0.00011</v>
+        <v>0.000142</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.077699</v>
+        <v>0.001785</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0</v>
+        <v>-0.000917</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.06128</v>
+        <v>0.018204</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.080066</v>
+        <v>-0.0005820000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -1416,7 +1348,7 @@
         <v>92240.17</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>0</v>
+        <v>7865.95</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>10.11</v>
@@ -1425,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>92240.17</v>
+        <v>100106.12</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>1</v>
@@ -1436,25 +1368,21 @@
       <c r="I19" s="4" t="n">
         <v>0.002474</v>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>EYDAP:ATSE:NO_PRICE</t>
-        </is>
-      </c>
+      <c r="J19" s="2" t="n"/>
       <c r="K19" s="4" t="n">
-        <v>0.00011</v>
+        <v>-0.000723</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.077598</v>
+        <v>0.001061</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0</v>
+        <v>-0.001639</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.07355399999999999</v>
+        <v>0.005105</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.080072</v>
+        <v>-0.001413</v>
       </c>
     </row>
     <row r="20">
@@ -1467,7 +1395,7 @@
         <v>92270.5</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0</v>
+        <v>7856.64</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>30.33</v>
@@ -1476,7 +1404,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>92270.5</v>
+        <v>100127.14</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>1</v>
@@ -1487,25 +1415,21 @@
       <c r="I20" s="4" t="n">
         <v>0.002798</v>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>EYDAP:ATSE:NO_PRICE</t>
-        </is>
-      </c>
+      <c r="J20" s="2" t="n"/>
       <c r="K20" s="4" t="n">
-        <v>0.000329</v>
+        <v>0.00021</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.077295</v>
+        <v>0.001271</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0</v>
+        <v>-0.00143</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.077263</v>
+        <v>0.001303</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.080093</v>
+        <v>-0.001527</v>
       </c>
     </row>
     <row r="21">
@@ -1518,7 +1442,7 @@
         <v>92280.61</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>8009.57</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>10.11</v>
@@ -1527,7 +1451,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>92280.61</v>
+        <v>100290.18</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>1</v>
@@ -1538,25 +1462,21 @@
       <c r="I21" s="4" t="n">
         <v>0.002905</v>
       </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>EYDAP:ATSE:NO_PRICE</t>
-        </is>
-      </c>
+      <c r="J21" s="2" t="n"/>
       <c r="K21" s="4" t="n">
-        <v>0.00011</v>
+        <v>0.001628</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.077194</v>
+        <v>0.002902</v>
       </c>
       <c r="M21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.087496</v>
+        <v>-0.0074</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.080099</v>
+        <v>-3e-06</v>
       </c>
     </row>
     <row r="22">
@@ -1569,7 +1489,7 @@
         <v>92290.72</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>0</v>
+        <v>7772.7</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>10.11</v>
@@ -1578,7 +1498,7 @@
         <v>0</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>92290.72</v>
+        <v>100063.42</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>1</v>
@@ -1589,25 +1509,21 @@
       <c r="I22" s="4" t="n">
         <v>0.003013</v>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>EYDAP:ATSE:NO_PRICE</t>
-        </is>
-      </c>
+      <c r="J22" s="2" t="n"/>
       <c r="K22" s="4" t="n">
-        <v>0.00011</v>
+        <v>-0.002261</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.07709299999999999</v>
+        <v>0.000634</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0</v>
+        <v>-0.002261</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.07692499999999999</v>
+        <v>0.000802</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.080106</v>
+        <v>-0.002379</v>
       </c>
     </row>
     <row r="23">
@@ -1620,7 +1536,7 @@
         <v>92300.83</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0</v>
+        <v>7544.12</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>10.11</v>
@@ -1629,7 +1545,7 @@
         <v>0</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>92300.83</v>
+        <v>99844.95</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>1</v>
@@ -1640,25 +1556,21 @@
       <c r="I23" s="4" t="n">
         <v>0.003121</v>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>EYDAP:ATSE:NO_PRICE</t>
-        </is>
-      </c>
+      <c r="J23" s="2" t="n"/>
       <c r="K23" s="4" t="n">
-        <v>0.00011</v>
+        <v>-0.002183</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.076992</v>
+        <v>-0.001551</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0</v>
+        <v>-0.004439</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.07424</v>
+        <v>0.001201</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.080113</v>
+        <v>-0.004672</v>
       </c>
     </row>
     <row r="24">
@@ -1671,7 +1583,7 @@
         <v>92310.95</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>0</v>
+        <v>7651.28</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>10.12</v>
@@ -1680,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>92310.95</v>
+        <v>99962.23</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>1</v>
@@ -1691,89 +1603,81 @@
       <c r="I24" s="4" t="n">
         <v>0.003229</v>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>EYDAP:ATSE:NO_PRICE</t>
-        </is>
-      </c>
+      <c r="J24" s="2" t="n"/>
       <c r="K24" s="4" t="n">
-        <v>0.00011</v>
+        <v>0.001175</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.076891</v>
+        <v>-0.000378</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0</v>
+        <v>-0.00327</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.07917</v>
+        <v>-0.002657</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.08012</v>
+        <v>-0.003607</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>92351.41</v>
+        <v>92341.3</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>0</v>
+        <v>7892.86</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>40.47</v>
+        <v>30.35</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>92351.41</v>
+        <v>100234.16</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.002279</v>
+        <v>0.004115</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.00366</v>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>EYDAP:ATSE:NO_PRICE</t>
-        </is>
-      </c>
+        <v>0.003552</v>
+      </c>
+      <c r="J25" s="2" t="n"/>
       <c r="K25" s="4" t="n">
-        <v>0.000438</v>
+        <v>0.00272</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.076486</v>
+        <v>0.002342</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0</v>
+        <v>-0.000559</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.078765</v>
+        <v>-0.001773</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.080146</v>
+        <v>-0.00121</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>92361.53999999999</v>
+        <v>92351.42</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>0</v>
+        <v>8445.65</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>10.12</v>
@@ -1782,7 +1686,7 @@
         <v>0</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>92361.53999999999</v>
+        <v>100797.06</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>1</v>
@@ -1791,40 +1695,36 @@
         <v>0.002279</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.003768</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>EYDAP:ATSE:NO_PRICE</t>
-        </is>
-      </c>
+        <v>0.00366</v>
+      </c>
+      <c r="J26" s="2" t="n"/>
       <c r="K26" s="4" t="n">
-        <v>0.00011</v>
+        <v>0.005616</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.07638499999999999</v>
+        <v>0.007971000000000001</v>
       </c>
       <c r="M26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.078664</v>
+        <v>0.005692</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.080153</v>
+        <v>0.004311</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>92371.66</v>
+        <v>92361.53999999999</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0</v>
+        <v>8466.459999999999</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>10.12</v>
@@ -1833,49 +1733,45 @@
         <v>0</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>92371.66</v>
+        <v>100828</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.002279</v>
+        <v>-0.003636</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.003876</v>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>EYDAP:ATSE:NO_PRICE</t>
-        </is>
-      </c>
+        <v>0.003768</v>
+      </c>
+      <c r="J27" s="2" t="n"/>
       <c r="K27" s="4" t="n">
-        <v>0.00011</v>
+        <v>0.000307</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.076283</v>
+        <v>0.008279999999999999</v>
       </c>
       <c r="M27" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.07856200000000001</v>
+        <v>0.011916</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.08015899999999999</v>
+        <v>0.004512</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>92381.78</v>
+        <v>92371.66</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>8548.530000000001</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>10.12</v>
@@ -1884,138 +1780,220 @@
         <v>0</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>92381.78</v>
+        <v>100920.19</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.002279</v>
+        <v>-0.004044</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.003984</v>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>EYDAP:ATSE:NO_PRICE</t>
-        </is>
-      </c>
+        <v>0.003876</v>
+      </c>
+      <c r="J28" s="2" t="n"/>
       <c r="K28" s="4" t="n">
-        <v>0.00011</v>
+        <v>0.000914</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.076182</v>
+        <v>0.009202</v>
       </c>
       <c r="M28" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.078461</v>
+        <v>0.013246</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.080166</v>
+        <v>0.005326</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>92422.28</v>
+        <v>92381.78</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0</v>
+        <v>8623.93</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>40.5</v>
+        <v>10.12</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>92422.28</v>
+        <v>101005.71</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.002279</v>
+        <v>-0.0018</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.004415</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>EYDAP:ATSE:NO_PRICE</t>
-        </is>
-      </c>
+        <v>0.003984</v>
+      </c>
+      <c r="J29" s="2" t="n"/>
       <c r="K29" s="4" t="n">
-        <v>0.000438</v>
+        <v>0.000847</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.075777</v>
+        <v>0.010057</v>
       </c>
       <c r="M29" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.078056</v>
+        <v>0.011857</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.080192</v>
+        <v>0.006073</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>92432.39999999999</v>
+        <v>92412.16</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>0</v>
+        <v>8622.860000000001</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>10.13</v>
+        <v>30.37</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>92432.39999999999</v>
+        <v>101035.02</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.002279</v>
+        <v>-0.003364</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.004523</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>EYDAP:ATSE:NO_PRICE</t>
-        </is>
-      </c>
+        <v>0.004307</v>
+      </c>
+      <c r="J30" s="2" t="n"/>
       <c r="K30" s="4" t="n">
-        <v>0.000109</v>
+        <v>0.00029</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.07567599999999999</v>
+        <v>0.01035</v>
       </c>
       <c r="M30" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.077955</v>
+        <v>0.013714</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.08019900000000001</v>
+        <v>0.006043</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>92422.28</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>8657.59</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>10.13</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>101079.87</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>-0.003772</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>0.004415</v>
+      </c>
+      <c r="J31" s="2" t="n"/>
+      <c r="K31" s="4" t="n">
+        <v>0.000444</v>
+      </c>
+      <c r="L31" s="4" t="n">
+        <v>0.010799</v>
+      </c>
+      <c r="M31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="4" t="n">
+        <v>0.014571</v>
+      </c>
+      <c r="O31" s="4" t="n">
+        <v>0.006384</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>101303.98</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>10.13</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>8871.57</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>101303.98</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>0.001259</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>0.004523</v>
+      </c>
+      <c r="J32" s="2" t="n"/>
+      <c r="K32" s="4" t="n">
+        <v>0.002217</v>
+      </c>
+      <c r="L32" s="4" t="n">
+        <v>0.01304</v>
+      </c>
+      <c r="M32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="4" t="n">
+        <v>0.011781</v>
+      </c>
+      <c r="O32" s="4" t="n">
+        <v>0.008517</v>
       </c>
     </row>
   </sheetData>
@@ -2168,7 +2146,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>paper</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -2182,13 +2160,17 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>569</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>7992.01</v>
-      </c>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="2" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="5" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
       <c r="K2" s="3" t="n"/>
       <c r="L2" s="3" t="n"/>
       <c r="M2" s="4" t="n"/>
@@ -2196,7 +2178,9 @@
       <c r="O2" s="5" t="n">
         <v>15.3</v>
       </c>
-      <c r="P2" s="4" t="n"/>
+      <c r="P2" s="4" t="n">
+        <v>0.096</v>
+      </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -2247,11 +2231,11 @@
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="5" t="n">
-        <v>40</v>
+        <v>41.110001</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="K3" s="3" t="n"/>
@@ -2304,11 +2288,11 @@
       </c>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="5" t="n">
-        <v>3.82</v>
+        <v>3.68</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="K4" s="3" t="n"/>
@@ -2332,7 +2316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2462,6 +2446,60 @@
       <c r="L2" s="2" t="inlineStr">
         <is>
           <t>Entry at 9 Sep close per Yahoo; memo W37 quoted the 4 Sep close of 12.28 as reference only</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2026-W43</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP:ATSE</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>569</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>13.94</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>1.122965</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Exit: H1 2026 run-rate EBITDA about EUR85m vs EUR150m underwritten; price above revised own fair value of about EUR10.7; catalyst date passed</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>2026-W43.md</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>PRICE 13.94 = Boerse Stuttgart quote 21 Oct 2026 as proxy for the ATSE close; replace with the ATSE 21 Oct close once the backfill lands and keep the date</t>
         </is>
       </c>
     </row>
@@ -2661,7 +2699,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>paper position</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -2669,7 +2707,11 @@
           <t>2026-W37.md</t>
         </is>
       </c>
-      <c r="N2" s="2" t="n"/>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Exited 2026-10-21 at EUR13.94 (proxy for ATSE close); about +16% in EUR; memos/2026-W43.md</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -2982,7 +3024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3043,6 +3085,49 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP:ATSE</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>7992.01</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>8871.57</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Y (H1 published 24 Sep; revenue EUR203.2m vs kill at 200)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Run-rate EBITDA half of what was underwritten yet price +16%; sold because own revised fair value (about EUR10.7) is below market and the catalyst had passed</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Underwrite regulatory revenue from the decision text not from a management briefing; the market re-rated on regime change not on run-rate EBITDA. A price gap went unmarked for six weeks: audit the feed weekly</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3054,14 +3139,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E233"/>
+  <dimension ref="A1:F249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3082,10 +3168,15 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>close_date</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>source</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
@@ -3105,12 +3196,13 @@
       <c r="C2" s="5" t="n">
         <v>0.195921</v>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3130,12 +3222,13 @@
       <c r="C3" s="5" t="n">
         <v>1.236033</v>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3155,12 +3248,13 @@
       <c r="C4" s="5" t="n">
         <v>1.163873</v>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3177,15 +3271,22 @@
           <t>EYDAP.AT</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n"/>
+      <c r="C5" s="5" t="n">
+        <v>12.02</v>
+      </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-09-09</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -3203,12 +3304,13 @@
       <c r="C6" s="5" t="n">
         <v>1.355142</v>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3228,12 +3330,13 @@
       <c r="C7" s="5" t="n">
         <v>146.559998</v>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3253,12 +3356,13 @@
       <c r="C8" s="5" t="n">
         <v>3.64</v>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D8" s="2" t="n"/>
       <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3278,12 +3382,13 @@
       <c r="C9" s="5" t="n">
         <v>35.080002</v>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3303,12 +3408,13 @@
       <c r="C10" s="5" t="n">
         <v>0.195856</v>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D10" s="2" t="n"/>
       <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3328,12 +3434,13 @@
       <c r="C11" s="5" t="n">
         <v>1.230254</v>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3353,12 +3460,13 @@
       <c r="C12" s="5" t="n">
         <v>1.161305</v>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D12" s="2" t="n"/>
       <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3375,15 +3483,22 @@
           <t>EYDAP.AT</t>
         </is>
       </c>
-      <c r="C13" s="5" t="n"/>
+      <c r="C13" s="5" t="n">
+        <v>12.02</v>
+      </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-09-10</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -3401,12 +3516,13 @@
       <c r="C14" s="5" t="n">
         <v>1.351151</v>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3426,12 +3542,13 @@
       <c r="C15" s="5" t="n">
         <v>145.830002</v>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D15" s="2" t="n"/>
       <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3451,12 +3568,13 @@
       <c r="C16" s="5" t="n">
         <v>3.75</v>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3476,12 +3594,13 @@
       <c r="C17" s="5" t="n">
         <v>35.810001</v>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3501,12 +3620,13 @@
       <c r="C18" s="5" t="n">
         <v>0.195111</v>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3526,12 +3646,13 @@
       <c r="C19" s="5" t="n">
         <v>1.22534</v>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D19" s="2" t="n"/>
       <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3551,12 +3672,13 @@
       <c r="C20" s="5" t="n">
         <v>1.160227</v>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3573,15 +3695,22 @@
           <t>EYDAP.AT</t>
         </is>
       </c>
-      <c r="C21" s="5" t="n"/>
+      <c r="C21" s="5" t="n">
+        <v>12</v>
+      </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-09-11</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -3599,12 +3728,13 @@
       <c r="C22" s="5" t="n">
         <v>1.352887</v>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3624,12 +3754,13 @@
       <c r="C23" s="5" t="n">
         <v>146.960007</v>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D23" s="2" t="n"/>
       <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3649,12 +3780,13 @@
       <c r="C24" s="5" t="n">
         <v>3.77</v>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D24" s="2" t="n"/>
       <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3674,12 +3806,13 @@
       <c r="C25" s="5" t="n">
         <v>34.560001</v>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D25" s="2" t="n"/>
       <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3699,12 +3832,13 @@
       <c r="C26" s="5" t="n">
         <v>0.194322</v>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3724,12 +3858,13 @@
       <c r="C27" s="5" t="n">
         <v>1.22471</v>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D27" s="2" t="n"/>
       <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3749,12 +3884,13 @@
       <c r="C28" s="5" t="n">
         <v>1.155402</v>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D28" s="2" t="n"/>
       <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3771,15 +3907,22 @@
           <t>EYDAP.AT</t>
         </is>
       </c>
-      <c r="C29" s="5" t="n"/>
+      <c r="C29" s="5" t="n">
+        <v>11.58</v>
+      </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-09-14</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3940,13 @@
       <c r="C30" s="5" t="n">
         <v>1.34991</v>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D30" s="2" t="n"/>
       <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3822,12 +3966,13 @@
       <c r="C31" s="5" t="n">
         <v>145.960007</v>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D31" s="2" t="n"/>
       <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3847,12 +3992,13 @@
       <c r="C32" s="5" t="n">
         <v>3.75</v>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D32" s="2" t="n"/>
       <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3872,12 +4018,13 @@
       <c r="C33" s="5" t="n">
         <v>34.740002</v>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D33" s="2" t="n"/>
       <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3897,12 +4044,13 @@
       <c r="C34" s="5" t="n">
         <v>0.194047</v>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D34" s="2" t="n"/>
       <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3922,12 +4070,13 @@
       <c r="C35" s="5" t="n">
         <v>1.222046</v>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D35" s="2" t="n"/>
       <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3947,12 +4096,13 @@
       <c r="C36" s="5" t="n">
         <v>1.154068</v>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D36" s="2" t="n"/>
       <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -3969,15 +4119,22 @@
           <t>EYDAP.AT</t>
         </is>
       </c>
-      <c r="C37" s="5" t="n"/>
+      <c r="C37" s="5" t="n">
+        <v>11.8</v>
+      </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-09-15</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -3995,12 +4152,13 @@
       <c r="C38" s="5" t="n">
         <v>1.347491</v>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D38" s="2" t="n"/>
       <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4020,12 +4178,13 @@
       <c r="C39" s="5" t="n">
         <v>145.210007</v>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D39" s="2" t="n"/>
       <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4045,12 +4204,13 @@
       <c r="C40" s="5" t="n">
         <v>3.7</v>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D40" s="2" t="n"/>
       <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4070,12 +4230,13 @@
       <c r="C41" s="5" t="n">
         <v>34.349998</v>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D41" s="2" t="n"/>
       <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4095,12 +4256,13 @@
       <c r="C42" s="5" t="n">
         <v>0.194194</v>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D42" s="2" t="n"/>
       <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4120,12 +4282,13 @@
       <c r="C43" s="5" t="n">
         <v>1.212004</v>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D43" s="2" t="n"/>
       <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4145,12 +4308,13 @@
       <c r="C44" s="5" t="n">
         <v>1.146526</v>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D44" s="2" t="n"/>
       <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4167,15 +4331,22 @@
           <t>EYDAP.AT</t>
         </is>
       </c>
-      <c r="C45" s="5" t="n"/>
+      <c r="C45" s="5" t="n">
+        <v>12.28</v>
+      </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-09-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -4193,12 +4364,13 @@
       <c r="C46" s="5" t="n">
         <v>1.338097</v>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D46" s="2" t="n"/>
       <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4218,12 +4390,13 @@
       <c r="C47" s="5" t="n">
         <v>145.889999</v>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D47" s="2" t="n"/>
       <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4243,12 +4416,13 @@
       <c r="C48" s="5" t="n">
         <v>3.62</v>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D48" s="2" t="n"/>
       <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4268,12 +4442,13 @@
       <c r="C49" s="5" t="n">
         <v>34.099998</v>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D49" s="2" t="n"/>
       <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4293,12 +4468,13 @@
       <c r="C50" s="5" t="n">
         <v>0.195145</v>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D50" s="2" t="n"/>
       <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4318,12 +4494,13 @@
       <c r="C51" s="5" t="n">
         <v>1.213931</v>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D51" s="2" t="n"/>
       <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4343,12 +4520,13 @@
       <c r="C52" s="5" t="n">
         <v>1.148106</v>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D52" s="2" t="n"/>
       <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4365,15 +4543,22 @@
           <t>EYDAP.AT</t>
         </is>
       </c>
-      <c r="C53" s="5" t="n"/>
+      <c r="C53" s="5" t="n">
+        <v>12.36</v>
+      </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-09-17</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -4391,12 +4576,13 @@
       <c r="C54" s="5" t="n">
         <v>1.335863</v>
       </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D54" s="2" t="n"/>
       <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4416,12 +4602,13 @@
       <c r="C55" s="5" t="n">
         <v>146.220001</v>
       </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D55" s="2" t="n"/>
       <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4441,12 +4628,13 @@
       <c r="C56" s="5" t="n">
         <v>3.55</v>
       </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D56" s="2" t="n"/>
       <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4466,12 +4654,13 @@
       <c r="C57" s="5" t="n">
         <v>34.110001</v>
       </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D57" s="2" t="n"/>
       <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4491,12 +4680,13 @@
       <c r="C58" s="5" t="n">
         <v>0.194424</v>
       </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D58" s="2" t="n"/>
       <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4516,12 +4706,13 @@
       <c r="C59" s="5" t="n">
         <v>1.216826</v>
       </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D59" s="2" t="n"/>
       <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4541,12 +4732,13 @@
       <c r="C60" s="5" t="n">
         <v>1.148897</v>
       </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D60" s="2" t="n"/>
       <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4563,15 +4755,22 @@
           <t>EYDAP.AT</t>
         </is>
       </c>
-      <c r="C61" s="5" t="n"/>
+      <c r="C61" s="5" t="n">
+        <v>12.48</v>
+      </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-09-18</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -4589,12 +4788,13 @@
       <c r="C62" s="5" t="n">
         <v>1.339351</v>
       </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D62" s="2" t="n"/>
       <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4614,12 +4814,13 @@
       <c r="C63" s="5" t="n">
         <v>145.690002</v>
       </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D63" s="2" t="n"/>
       <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4639,12 +4840,13 @@
       <c r="C64" s="5" t="n">
         <v>3.62</v>
       </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D64" s="2" t="n"/>
       <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4664,12 +4866,13 @@
       <c r="C65" s="5" t="n">
         <v>34.509998</v>
       </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D65" s="2" t="n"/>
       <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4689,12 +4892,13 @@
       <c r="C66" s="5" t="n">
         <v>0.195595</v>
       </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D66" s="2" t="n"/>
       <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4714,12 +4918,13 @@
       <c r="C67" s="5" t="n">
         <v>1.218621</v>
       </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D67" s="2" t="n"/>
       <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4739,12 +4944,13 @@
       <c r="C68" s="5" t="n">
         <v>1.146657</v>
       </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D68" s="2" t="n"/>
       <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4761,15 +4967,22 @@
           <t>EYDAP.AT</t>
         </is>
       </c>
-      <c r="C69" s="5" t="n"/>
+      <c r="C69" s="5" t="n">
+        <v>12.2</v>
+      </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-09-21</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -4787,12 +5000,13 @@
       <c r="C70" s="5" t="n">
         <v>1.337041</v>
       </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D70" s="2" t="n"/>
       <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4812,12 +5026,13 @@
       <c r="C71" s="5" t="n">
         <v>147.460007</v>
       </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D71" s="2" t="n"/>
       <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4837,12 +5052,13 @@
       <c r="C72" s="5" t="n">
         <v>3.59</v>
       </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D72" s="2" t="n"/>
       <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4862,12 +5078,13 @@
       <c r="C73" s="5" t="n">
         <v>35.349998</v>
       </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D73" s="2" t="n"/>
       <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4887,12 +5104,13 @@
       <c r="C74" s="5" t="n">
         <v>0.19604</v>
       </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D74" s="2" t="n"/>
       <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4912,12 +5130,13 @@
       <c r="C75" s="5" t="n">
         <v>1.219988</v>
       </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D75" s="2" t="n"/>
       <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4937,12 +5156,13 @@
       <c r="C76" s="5" t="n">
         <v>1.145082</v>
       </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D76" s="2" t="n"/>
       <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -4959,15 +5179,22 @@
           <t>EYDAP.AT</t>
         </is>
       </c>
-      <c r="C77" s="5" t="n"/>
+      <c r="C77" s="5" t="n">
+        <v>12.48</v>
+      </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-09-22</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -4985,12 +5212,13 @@
       <c r="C78" s="5" t="n">
         <v>1.334917</v>
       </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D78" s="2" t="n"/>
       <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5010,12 +5238,13 @@
       <c r="C79" s="5" t="n">
         <v>147.960007</v>
       </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D79" s="2" t="n"/>
       <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5035,12 +5264,13 @@
       <c r="C80" s="5" t="n">
         <v>3.6</v>
       </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D80" s="2" t="n"/>
       <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5060,12 +5290,13 @@
       <c r="C81" s="5" t="n">
         <v>34.810001</v>
       </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D81" s="2" t="n"/>
       <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5085,12 +5316,13 @@
       <c r="C82" s="5" t="n">
         <v>0.193558</v>
       </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D82" s="2" t="n"/>
       <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5110,12 +5342,13 @@
       <c r="C83" s="5" t="n">
         <v>1.213136</v>
       </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D83" s="2" t="n"/>
       <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5135,12 +5368,13 @@
       <c r="C84" s="5" t="n">
         <v>1.138952</v>
       </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D84" s="2" t="n"/>
       <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5157,15 +5391,22 @@
           <t>EYDAP.AT</t>
         </is>
       </c>
-      <c r="C85" s="5" t="n"/>
+      <c r="C85" s="5" t="n">
+        <v>12.24</v>
+      </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-09-23</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5424,13 @@
       <c r="C86" s="5" t="n">
         <v>1.324661</v>
       </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D86" s="2" t="n"/>
       <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5208,12 +5450,13 @@
       <c r="C87" s="5" t="n">
         <v>147.009995</v>
       </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D87" s="2" t="n"/>
       <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5233,12 +5476,13 @@
       <c r="C88" s="5" t="n">
         <v>3.5</v>
       </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D88" s="2" t="n"/>
       <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5258,12 +5502,13 @@
       <c r="C89" s="5" t="n">
         <v>34.040001</v>
       </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D89" s="2" t="n"/>
       <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5283,12 +5528,13 @@
       <c r="C90" s="5" t="n">
         <v>0.192626</v>
       </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D90" s="2" t="n"/>
       <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5308,12 +5554,13 @@
       <c r="C91" s="5" t="n">
         <v>1.209292</v>
       </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D91" s="2" t="n"/>
       <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5333,12 +5580,13 @@
       <c r="C92" s="5" t="n">
         <v>1.138174</v>
       </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D92" s="2" t="n"/>
       <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5355,15 +5603,22 @@
           <t>EYDAP.AT</t>
         </is>
       </c>
-      <c r="C93" s="5" t="n"/>
+      <c r="C93" s="5" t="n">
+        <v>12.12</v>
+      </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-09-24</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -5381,12 +5636,13 @@
       <c r="C94" s="5" t="n">
         <v>1.321528</v>
       </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D94" s="2" t="n"/>
       <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5406,12 +5662,13 @@
       <c r="C95" s="5" t="n">
         <v>145.899994</v>
       </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D95" s="2" t="n"/>
       <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5431,12 +5688,13 @@
       <c r="C96" s="5" t="n">
         <v>3.45</v>
       </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D96" s="2" t="n"/>
       <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5456,12 +5714,13 @@
       <c r="C97" s="5" t="n">
         <v>33.560001</v>
       </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D97" s="2" t="n"/>
       <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5481,12 +5740,13 @@
       <c r="C98" s="5" t="n">
         <v>0.192805</v>
       </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D98" s="2" t="n"/>
       <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5506,12 +5766,13 @@
       <c r="C99" s="5" t="n">
         <v>1.207292</v>
       </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D99" s="2" t="n"/>
       <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5531,12 +5792,13 @@
       <c r="C100" s="5" t="n">
         <v>1.139212</v>
       </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D100" s="2" t="n"/>
       <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5553,15 +5815,22 @@
           <t>EYDAP.AT</t>
         </is>
       </c>
-      <c r="C101" s="5" t="n"/>
+      <c r="C101" s="5" t="n">
+        <v>12.16</v>
+      </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-09-25</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -5579,12 +5848,13 @@
       <c r="C102" s="5" t="n">
         <v>1.324644</v>
       </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D102" s="2" t="n"/>
       <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5604,12 +5874,13 @@
       <c r="C103" s="5" t="n">
         <v>146.910004</v>
       </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D103" s="2" t="n"/>
       <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5629,12 +5900,13 @@
       <c r="C104" s="5" t="n">
         <v>3.49</v>
       </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D104" s="2" t="n"/>
       <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5654,12 +5926,13 @@
       <c r="C105" s="5" t="n">
         <v>33.349998</v>
       </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D105" s="2" t="n"/>
       <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5679,12 +5952,13 @@
       <c r="C106" s="5" t="n">
         <v>0.191435</v>
       </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D106" s="2" t="n"/>
       <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5704,12 +5978,13 @@
       <c r="C107" s="5" t="n">
         <v>1.202776</v>
       </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D107" s="2" t="n"/>
       <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5729,12 +6004,13 @@
       <c r="C108" s="5" t="n">
         <v>1.137398</v>
       </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D108" s="2" t="n"/>
       <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5751,15 +6027,22 @@
           <t>EYDAP.AT</t>
         </is>
       </c>
-      <c r="C109" s="5" t="n"/>
+      <c r="C109" s="5" t="n">
+        <v>12.44</v>
+      </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-09-28</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -5777,12 +6060,13 @@
       <c r="C110" s="5" t="n">
         <v>1.325574</v>
       </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D110" s="2" t="n"/>
       <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5802,12 +6086,13 @@
       <c r="C111" s="5" t="n">
         <v>146.179993</v>
       </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D111" s="2" t="n"/>
       <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5827,12 +6112,13 @@
       <c r="C112" s="5" t="n">
         <v>3.5</v>
       </c>
-      <c r="D112" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D112" s="2" t="n"/>
       <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5852,12 +6138,13 @@
       <c r="C113" s="5" t="n">
         <v>33.040001</v>
       </c>
-      <c r="D113" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D113" s="2" t="n"/>
       <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5877,12 +6164,13 @@
       <c r="C114" s="5" t="n">
         <v>0.192193</v>
       </c>
-      <c r="D114" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D114" s="2" t="n"/>
       <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5902,12 +6190,13 @@
       <c r="C115" s="5" t="n">
         <v>1.200538</v>
       </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D115" s="2" t="n"/>
       <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5927,12 +6216,13 @@
       <c r="C116" s="5" t="n">
         <v>1.134687</v>
       </c>
-      <c r="D116" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D116" s="2" t="n"/>
       <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -5949,15 +6239,22 @@
           <t>EYDAP.AT</t>
         </is>
       </c>
-      <c r="C117" s="5" t="n"/>
+      <c r="C117" s="5" t="n">
+        <v>12.34</v>
+      </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-09-29</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -5975,12 +6272,13 @@
       <c r="C118" s="5" t="n">
         <v>1.322891</v>
       </c>
-      <c r="D118" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D118" s="2" t="n"/>
       <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6000,12 +6298,13 @@
       <c r="C119" s="5" t="n">
         <v>145.869995</v>
       </c>
-      <c r="D119" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D119" s="2" t="n"/>
       <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6025,12 +6324,13 @@
       <c r="C120" s="5" t="n">
         <v>3.65</v>
       </c>
-      <c r="D120" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D120" s="2" t="n"/>
       <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6050,12 +6350,13 @@
       <c r="C121" s="5" t="n">
         <v>32.939999</v>
       </c>
-      <c r="D121" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D121" s="2" t="n"/>
       <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6075,12 +6376,13 @@
       <c r="C122" s="5" t="n">
         <v>0.192957</v>
       </c>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D122" s="2" t="n"/>
       <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6100,12 +6402,13 @@
       <c r="C123" s="5" t="n">
         <v>1.198538</v>
       </c>
-      <c r="D123" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D123" s="2" t="n"/>
       <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6125,12 +6428,13 @@
       <c r="C124" s="5" t="n">
         <v>1.133273</v>
       </c>
-      <c r="D124" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D124" s="2" t="n"/>
       <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6147,15 +6451,22 @@
           <t>EYDAP.AT</t>
         </is>
       </c>
-      <c r="C125" s="5" t="n"/>
+      <c r="C125" s="5" t="n">
+        <v>12.32</v>
+      </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-09-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -6173,12 +6484,13 @@
       <c r="C126" s="5" t="n">
         <v>1.32714</v>
       </c>
-      <c r="D126" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D126" s="2" t="n"/>
       <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6198,12 +6510,13 @@
       <c r="C127" s="5" t="n">
         <v>146.679993</v>
       </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D127" s="2" t="n"/>
       <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6223,12 +6536,13 @@
       <c r="C128" s="5" t="n">
         <v>3.72</v>
       </c>
-      <c r="D128" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D128" s="2" t="n"/>
       <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6248,12 +6562,13 @@
       <c r="C129" s="5" t="n">
         <v>33.009998</v>
       </c>
-      <c r="D129" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D129" s="2" t="n"/>
       <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6273,12 +6588,13 @@
       <c r="C130" s="5" t="n">
         <v>0.191479</v>
       </c>
-      <c r="D130" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D130" s="2" t="n"/>
       <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6298,12 +6614,13 @@
       <c r="C131" s="5" t="n">
         <v>1.204021</v>
       </c>
-      <c r="D131" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D131" s="2" t="n"/>
       <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6323,12 +6640,13 @@
       <c r="C132" s="5" t="n">
         <v>1.124733</v>
       </c>
-      <c r="D132" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D132" s="2" t="n"/>
       <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6345,15 +6663,22 @@
           <t>EYDAP.AT</t>
         </is>
       </c>
-      <c r="C133" s="5" t="n"/>
+      <c r="C133" s="5" t="n">
+        <v>12.42</v>
+      </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-10-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -6371,12 +6696,13 @@
       <c r="C134" s="5" t="n">
         <v>1.319906</v>
       </c>
-      <c r="D134" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D134" s="2" t="n"/>
       <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6396,12 +6722,13 @@
       <c r="C135" s="5" t="n">
         <v>144.660004</v>
       </c>
-      <c r="D135" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D135" s="2" t="n"/>
       <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6421,12 +6748,13 @@
       <c r="C136" s="5" t="n">
         <v>3.67</v>
       </c>
-      <c r="D136" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D136" s="2" t="n"/>
       <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6446,12 +6774,13 @@
       <c r="C137" s="5" t="n">
         <v>33.59</v>
       </c>
-      <c r="D137" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D137" s="2" t="n"/>
       <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6471,12 +6800,13 @@
       <c r="C138" s="5" t="n">
         <v>0.191674</v>
       </c>
-      <c r="D138" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D138" s="2" t="n"/>
       <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6496,12 +6826,13 @@
       <c r="C139" s="5" t="n">
         <v>1.20703</v>
       </c>
-      <c r="D139" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D139" s="2" t="n"/>
       <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6521,12 +6852,13 @@
       <c r="C140" s="5" t="n">
         <v>1.125746</v>
       </c>
-      <c r="D140" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D140" s="2" t="n"/>
       <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6543,15 +6875,22 @@
           <t>EYDAP.AT</t>
         </is>
       </c>
-      <c r="C141" s="5" t="n"/>
+      <c r="C141" s="5" t="n">
+        <v>12.28</v>
+      </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-10-02</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6908,13 @@
       <c r="C142" s="5" t="n">
         <v>1.324047</v>
       </c>
-      <c r="D142" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D142" s="2" t="n"/>
       <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6594,12 +6934,13 @@
       <c r="C143" s="5" t="n">
         <v>146.479996</v>
       </c>
-      <c r="D143" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D143" s="2" t="n"/>
       <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6619,12 +6960,13 @@
       <c r="C144" s="5" t="n">
         <v>3.77</v>
       </c>
-      <c r="D144" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D144" s="2" t="n"/>
       <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6644,12 +6986,13 @@
       <c r="C145" s="5" t="n">
         <v>35.209999</v>
       </c>
-      <c r="D145" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D145" s="2" t="n"/>
       <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6669,12 +7012,13 @@
       <c r="C146" s="5" t="n">
         <v>0.200212</v>
       </c>
-      <c r="D146" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D146" s="2" t="n"/>
       <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6694,12 +7038,13 @@
       <c r="C147" s="5" t="n">
         <v>1.203949</v>
       </c>
-      <c r="D147" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D147" s="2" t="n"/>
       <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6719,12 +7064,13 @@
       <c r="C148" s="5" t="n">
         <v>1.122586</v>
       </c>
-      <c r="D148" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D148" s="2" t="n"/>
       <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6741,15 +7087,22 @@
           <t>EYDAP.AT</t>
         </is>
       </c>
-      <c r="C149" s="5" t="n"/>
+      <c r="C149" s="5" t="n">
+        <v>12.3</v>
+      </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-10-05</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -6767,12 +7120,13 @@
       <c r="C150" s="5" t="n">
         <v>1.321825</v>
       </c>
-      <c r="D150" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D150" s="2" t="n"/>
       <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6792,12 +7146,13 @@
       <c r="C151" s="5" t="n">
         <v>147.070007</v>
       </c>
-      <c r="D151" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D151" s="2" t="n"/>
       <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6817,12 +7172,13 @@
       <c r="C152" s="5" t="n">
         <v>3.96</v>
       </c>
-      <c r="D152" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D152" s="2" t="n"/>
       <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6842,12 +7198,13 @@
       <c r="C153" s="5" t="n">
         <v>37.810001</v>
       </c>
-      <c r="D153" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D153" s="2" t="n"/>
       <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6867,12 +7224,13 @@
       <c r="C154" s="5" t="n">
         <v>0.200662</v>
       </c>
-      <c r="D154" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D154" s="2" t="n"/>
       <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6892,12 +7250,13 @@
       <c r="C155" s="5" t="n">
         <v>1.203138</v>
       </c>
-      <c r="D155" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D155" s="2" t="n"/>
       <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6917,12 +7276,13 @@
       <c r="C156" s="5" t="n">
         <v>1.126126</v>
       </c>
-      <c r="D156" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D156" s="2" t="n"/>
       <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6939,15 +7299,22 @@
           <t>EYDAP.AT</t>
         </is>
       </c>
-      <c r="C157" s="5" t="n"/>
+      <c r="C157" s="5" t="n">
+        <v>12.5</v>
+      </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-10-06</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -6965,12 +7332,13 @@
       <c r="C158" s="5" t="n">
         <v>1.327492</v>
       </c>
-      <c r="D158" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D158" s="2" t="n"/>
       <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -6990,12 +7358,13 @@
       <c r="C159" s="5" t="n">
         <v>148.589996</v>
       </c>
-      <c r="D159" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D159" s="2" t="n"/>
       <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7015,12 +7384,13 @@
       <c r="C160" s="5" t="n">
         <v>3.91</v>
       </c>
-      <c r="D160" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D160" s="2" t="n"/>
       <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7040,12 +7410,13 @@
       <c r="C161" s="5" t="n">
         <v>38.52</v>
       </c>
-      <c r="D161" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D161" s="2" t="n"/>
       <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7065,12 +7436,13 @@
       <c r="C162" s="5" t="n">
         <v>0.199132</v>
       </c>
-      <c r="D162" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D162" s="2" t="n"/>
       <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7090,12 +7462,13 @@
       <c r="C163" s="5" t="n">
         <v>1.20074</v>
       </c>
-      <c r="D163" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D163" s="2" t="n"/>
       <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7115,12 +7488,13 @@
       <c r="C164" s="5" t="n">
         <v>1.119695</v>
       </c>
-      <c r="D164" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D164" s="2" t="n"/>
       <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7137,15 +7511,22 @@
           <t>EYDAP.AT</t>
         </is>
       </c>
-      <c r="C165" s="5" t="n"/>
+      <c r="C165" s="5" t="n">
+        <v>12.2</v>
+      </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-10-07</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -7163,12 +7544,13 @@
       <c r="C166" s="5" t="n">
         <v>1.32165</v>
       </c>
-      <c r="D166" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D166" s="2" t="n"/>
       <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7188,12 +7570,13 @@
       <c r="C167" s="5" t="n">
         <v>147.050003</v>
       </c>
-      <c r="D167" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D167" s="2" t="n"/>
       <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7213,12 +7596,13 @@
       <c r="C168" s="5" t="n">
         <v>3.94</v>
       </c>
-      <c r="D168" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D168" s="2" t="n"/>
       <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7238,12 +7622,13 @@
       <c r="C169" s="5" t="n">
         <v>41.970001</v>
       </c>
-      <c r="D169" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D169" s="2" t="n"/>
       <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7263,12 +7648,13 @@
       <c r="C170" s="5" t="n">
         <v>0.199334</v>
       </c>
-      <c r="D170" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D170" s="2" t="n"/>
       <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7288,12 +7674,13 @@
       <c r="C171" s="5" t="n">
         <v>1.203427</v>
       </c>
-      <c r="D171" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D171" s="2" t="n"/>
       <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7313,12 +7700,13 @@
       <c r="C172" s="5" t="n">
         <v>1.121705</v>
       </c>
-      <c r="D172" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D172" s="2" t="n"/>
       <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7335,15 +7723,22 @@
           <t>EYDAP.AT</t>
         </is>
       </c>
-      <c r="C173" s="5" t="n"/>
+      <c r="C173" s="5" t="n">
+        <v>11.82</v>
+      </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-10-08</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -7361,12 +7756,13 @@
       <c r="C174" s="5" t="n">
         <v>1.323241</v>
       </c>
-      <c r="D174" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D174" s="2" t="n"/>
       <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7386,12 +7782,13 @@
       <c r="C175" s="5" t="n">
         <v>146.669998</v>
       </c>
-      <c r="D175" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D175" s="2" t="n"/>
       <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7411,12 +7808,13 @@
       <c r="C176" s="5" t="n">
         <v>3.85</v>
       </c>
-      <c r="D176" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D176" s="2" t="n"/>
       <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7436,12 +7834,13 @@
       <c r="C177" s="5" t="n">
         <v>43.049999</v>
       </c>
-      <c r="D177" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D177" s="2" t="n"/>
       <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7461,12 +7860,13 @@
       <c r="C178" s="5" t="n">
         <v>0.200349</v>
       </c>
-      <c r="D178" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D178" s="2" t="n"/>
       <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7486,12 +7886,13 @@
       <c r="C179" s="5" t="n">
         <v>1.204819</v>
       </c>
-      <c r="D179" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D179" s="2" t="n"/>
       <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7511,12 +7912,13 @@
       <c r="C180" s="5" t="n">
         <v>1.120574</v>
       </c>
-      <c r="D180" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D180" s="2" t="n"/>
       <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7533,15 +7935,22 @@
           <t>EYDAP.AT</t>
         </is>
       </c>
-      <c r="C181" s="5" t="n"/>
+      <c r="C181" s="5" t="n">
+        <v>12</v>
+      </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-10-09</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7968,13 @@
       <c r="C182" s="5" t="n">
         <v>1.323311</v>
       </c>
-      <c r="D182" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D182" s="2" t="n"/>
       <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7584,12 +7994,13 @@
       <c r="C183" s="5" t="n">
         <v>147.410004</v>
       </c>
-      <c r="D183" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D183" s="2" t="n"/>
       <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7609,12 +8020,13 @@
       <c r="C184" s="5" t="n">
         <v>3.94</v>
       </c>
-      <c r="D184" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D184" s="2" t="n"/>
       <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7634,12 +8046,13 @@
       <c r="C185" s="5" t="n">
         <v>45.07</v>
       </c>
-      <c r="D185" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+      <c r="D185" s="2" t="n"/>
       <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7648,7 +8061,7 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
@@ -7657,14 +8070,19 @@
         </is>
       </c>
       <c r="C186" s="5" t="n">
-        <v>0.20055</v>
+        <v>0.200566</v>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>yfinance</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7673,7 +8091,7 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
@@ -7682,14 +8100,19 @@
         </is>
       </c>
       <c r="C187" s="5" t="n">
-        <v>1.200509</v>
+        <v>1.204892</v>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>yfinance</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7698,7 +8121,7 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
@@ -7707,14 +8130,19 @@
         </is>
       </c>
       <c r="C188" s="5" t="n">
-        <v>1.117693</v>
+        <v>1.120473</v>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>yfinance</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7723,7 +8151,7 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
@@ -7731,22 +8159,29 @@
           <t>EYDAP.AT</t>
         </is>
       </c>
-      <c r="C189" s="5" t="n"/>
+      <c r="C189" s="5" t="n">
+        <v>12.38</v>
+      </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
@@ -7755,14 +8190,19 @@
         </is>
       </c>
       <c r="C190" s="5" t="n">
-        <v>1.321929</v>
+        <v>1.324152</v>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>yfinance</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7771,7 +8211,7 @@
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
@@ -7779,22 +8219,29 @@
           <t>IWDA.L</t>
         </is>
       </c>
-      <c r="C191" s="5" t="n"/>
+      <c r="C191" s="5" t="n">
+        <v>147.679993</v>
+      </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
@@ -7802,22 +8249,29 @@
           <t>LIGT3.SA</t>
         </is>
       </c>
-      <c r="C192" s="5" t="n"/>
+      <c r="C192" s="5" t="n">
+        <v>3.94</v>
+      </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-10-13</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>lagged</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
@@ -7825,22 +8279,29 @@
           <t>SAPR11.SA</t>
         </is>
       </c>
-      <c r="C193" s="5" t="n"/>
+      <c r="C193" s="5" t="n">
+        <v>45.07</v>
+      </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-10-13</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>lagged</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
@@ -7848,22 +8309,25 @@
           <t>BRLUSD=X</t>
         </is>
       </c>
-      <c r="C194" s="5" t="n"/>
-      <c r="D194" s="2" t="inlineStr">
-        <is>
-          <t>yfinance-no-close-on-2026-10-14</t>
-        </is>
-      </c>
+      <c r="C194" s="5" t="n">
+        <v>0.20055</v>
+      </c>
+      <c r="D194" s="2" t="n"/>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
@@ -7872,14 +8336,15 @@
         </is>
       </c>
       <c r="C195" s="5" t="n">
-        <v>1.200999</v>
-      </c>
-      <c r="D195" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+        <v>1.200509</v>
+      </c>
+      <c r="D195" s="2" t="n"/>
       <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7888,7 +8353,7 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
@@ -7897,14 +8362,15 @@
         </is>
       </c>
       <c r="C196" s="5" t="n">
-        <v>1.120448</v>
-      </c>
-      <c r="D196" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+        <v>1.117693</v>
+      </c>
+      <c r="D196" s="2" t="n"/>
       <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7913,7 +8379,7 @@
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
@@ -7921,22 +8387,29 @@
           <t>EYDAP.AT</t>
         </is>
       </c>
-      <c r="C197" s="5" t="n"/>
+      <c r="C197" s="5" t="n">
+        <v>13.28</v>
+      </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
@@ -7945,14 +8418,15 @@
         </is>
       </c>
       <c r="C198" s="5" t="n">
-        <v>1.325891</v>
-      </c>
-      <c r="D198" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+        <v>1.321929</v>
+      </c>
+      <c r="D198" s="2" t="n"/>
       <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -7961,7 +8435,7 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
@@ -7969,22 +8443,29 @@
           <t>IWDA.L</t>
         </is>
       </c>
-      <c r="C199" s="5" t="n"/>
+      <c r="C199" s="5" t="n">
+        <v>147.410004</v>
+      </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
@@ -7992,22 +8473,29 @@
           <t>LIGT3.SA</t>
         </is>
       </c>
-      <c r="C200" s="5" t="n"/>
+      <c r="C200" s="5" t="n">
+        <v>3.8</v>
+      </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
@@ -8015,22 +8503,29 @@
           <t>SAPR11.SA</t>
         </is>
       </c>
-      <c r="C201" s="5" t="n"/>
+      <c r="C201" s="5" t="n">
+        <v>41.299999</v>
+      </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
@@ -8039,14 +8534,19 @@
         </is>
       </c>
       <c r="C202" s="5" t="n">
-        <v>0.198432</v>
+        <v>0.198973</v>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>yfinance</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8055,7 +8555,7 @@
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
@@ -8064,14 +8564,15 @@
         </is>
       </c>
       <c r="C203" s="5" t="n">
-        <v>1.202501</v>
-      </c>
-      <c r="D203" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+        <v>1.200999</v>
+      </c>
+      <c r="D203" s="2" t="n"/>
       <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8080,7 +8581,7 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
@@ -8089,14 +8590,15 @@
         </is>
       </c>
       <c r="C204" s="5" t="n">
-        <v>1.119507</v>
-      </c>
-      <c r="D204" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+        <v>1.120448</v>
+      </c>
+      <c r="D204" s="2" t="n"/>
       <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8105,7 +8607,7 @@
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
@@ -8113,22 +8615,29 @@
           <t>EYDAP.AT</t>
         </is>
       </c>
-      <c r="C205" s="5" t="n"/>
+      <c r="C205" s="5" t="n">
+        <v>13.28</v>
+      </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
@@ -8137,14 +8646,15 @@
         </is>
       </c>
       <c r="C206" s="5" t="n">
-        <v>1.323014</v>
-      </c>
-      <c r="D206" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+        <v>1.325891</v>
+      </c>
+      <c r="D206" s="2" t="n"/>
       <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8153,7 +8663,7 @@
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
@@ -8161,22 +8671,29 @@
           <t>IWDA.L</t>
         </is>
       </c>
-      <c r="C207" s="5" t="n"/>
+      <c r="C207" s="5" t="n">
+        <v>146.539993</v>
+      </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
@@ -8185,14 +8702,19 @@
         </is>
       </c>
       <c r="C208" s="5" t="n">
-        <v>3.84</v>
+        <v>3.94</v>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>yfinance</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8201,7 +8723,7 @@
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
@@ -8210,14 +8732,19 @@
         </is>
       </c>
       <c r="C209" s="5" t="n">
-        <v>39.419998</v>
+        <v>40.900002</v>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>yfinance</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8226,7 +8753,7 @@
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
@@ -8235,14 +8762,15 @@
         </is>
       </c>
       <c r="C210" s="5" t="n">
-        <v>0.197266</v>
-      </c>
-      <c r="D210" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+        <v>0.198432</v>
+      </c>
+      <c r="D210" s="2" t="n"/>
       <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8251,7 +8779,7 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
@@ -8260,14 +8788,15 @@
         </is>
       </c>
       <c r="C211" s="5" t="n">
-        <v>1.214167</v>
-      </c>
-      <c r="D211" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+        <v>1.202501</v>
+      </c>
+      <c r="D211" s="2" t="n"/>
       <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8276,7 +8805,7 @@
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
@@ -8285,14 +8814,15 @@
         </is>
       </c>
       <c r="C212" s="5" t="n">
-        <v>1.124354</v>
-      </c>
-      <c r="D212" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+        <v>1.119507</v>
+      </c>
+      <c r="D212" s="2" t="n"/>
       <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8301,7 +8831,7 @@
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
@@ -8309,22 +8839,29 @@
           <t>EYDAP.AT</t>
         </is>
       </c>
-      <c r="C213" s="5" t="n"/>
+      <c r="C213" s="5" t="n">
+        <v>13.42</v>
+      </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
@@ -8333,14 +8870,15 @@
         </is>
       </c>
       <c r="C214" s="5" t="n">
-        <v>1.327316</v>
-      </c>
-      <c r="D214" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+        <v>1.323014</v>
+      </c>
+      <c r="D214" s="2" t="n"/>
       <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8349,7 +8887,7 @@
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
@@ -8357,22 +8895,29 @@
           <t>IWDA.L</t>
         </is>
       </c>
-      <c r="C215" s="5" t="n"/>
+      <c r="C215" s="5" t="n">
+        <v>146.479996</v>
+      </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
@@ -8381,14 +8926,15 @@
         </is>
       </c>
       <c r="C216" s="5" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="D216" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+        <v>3.84</v>
+      </c>
+      <c r="D216" s="2" t="n"/>
       <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8397,7 +8943,7 @@
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
@@ -8406,14 +8952,15 @@
         </is>
       </c>
       <c r="C217" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="D217" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+        <v>39.419998</v>
+      </c>
+      <c r="D217" s="2" t="n"/>
       <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8422,7 +8969,7 @@
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
@@ -8430,22 +8977,25 @@
           <t>BRLUSD=X</t>
         </is>
       </c>
-      <c r="C218" s="5" t="n"/>
-      <c r="D218" s="2" t="inlineStr">
-        <is>
-          <t>yfinance-no-close-on-2026-10-20</t>
-        </is>
-      </c>
+      <c r="C218" s="5" t="n">
+        <v>0.197266</v>
+      </c>
+      <c r="D218" s="2" t="n"/>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
@@ -8454,14 +9004,15 @@
         </is>
       </c>
       <c r="C219" s="5" t="n">
-        <v>1.210698</v>
-      </c>
-      <c r="D219" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+        <v>1.214167</v>
+      </c>
+      <c r="D219" s="2" t="n"/>
       <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8470,7 +9021,7 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
@@ -8479,14 +9030,15 @@
         </is>
       </c>
       <c r="C220" s="5" t="n">
-        <v>1.122083</v>
-      </c>
-      <c r="D220" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+        <v>1.124354</v>
+      </c>
+      <c r="D220" s="2" t="n"/>
       <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8495,7 +9047,7 @@
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
@@ -8503,22 +9055,29 @@
           <t>EYDAP.AT</t>
         </is>
       </c>
-      <c r="C221" s="5" t="n"/>
+      <c r="C221" s="5" t="n">
+        <v>13.48</v>
+      </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-10-20</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
@@ -8527,14 +9086,15 @@
         </is>
       </c>
       <c r="C222" s="5" t="n">
-        <v>1.33154</v>
-      </c>
-      <c r="D222" s="2" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
+        <v>1.327316</v>
+      </c>
+      <c r="D222" s="2" t="n"/>
       <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8543,7 +9103,7 @@
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
@@ -8551,22 +9111,29 @@
           <t>IWDA.L</t>
         </is>
       </c>
-      <c r="C223" s="5" t="n"/>
+      <c r="C223" s="5" t="n">
+        <v>146.809998</v>
+      </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-10-20</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
@@ -8574,22 +9141,25 @@
           <t>LIGT3.SA</t>
         </is>
       </c>
-      <c r="C224" s="5" t="n"/>
-      <c r="D224" s="2" t="inlineStr">
-        <is>
-          <t>yfinance-no-close-on-2026-10-20</t>
-        </is>
-      </c>
+      <c r="C224" s="5" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="D224" s="2" t="n"/>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
@@ -8597,22 +9167,25 @@
           <t>SAPR11.SA</t>
         </is>
       </c>
-      <c r="C225" s="5" t="n"/>
-      <c r="D225" s="2" t="inlineStr">
-        <is>
-          <t>yfinance-no-close-on-2026-10-20</t>
-        </is>
-      </c>
+      <c r="C225" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="D225" s="2" t="n"/>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
@@ -8620,22 +9193,29 @@
           <t>BRLUSD=X</t>
         </is>
       </c>
-      <c r="C226" s="5" t="n"/>
+      <c r="C226" s="5" t="n">
+        <v>0.197507</v>
+      </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-10-21</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
@@ -8644,14 +9224,19 @@
         </is>
       </c>
       <c r="C227" s="5" t="n">
-        <v>1.211284</v>
+        <v>1.213961</v>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>yfinance</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8660,7 +9245,7 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
@@ -8669,14 +9254,19 @@
         </is>
       </c>
       <c r="C228" s="5" t="n">
-        <v>1.122965</v>
+        <v>1.122549</v>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>yfinance</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8685,7 +9275,7 @@
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
@@ -8693,22 +9283,29 @@
           <t>EYDAP.AT</t>
         </is>
       </c>
-      <c r="C229" s="5" t="n"/>
+      <c r="C229" s="5" t="n">
+        <v>13.5</v>
+      </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-10-21</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
@@ -8717,14 +9314,19 @@
         </is>
       </c>
       <c r="C230" s="5" t="n">
-        <v>1.337453</v>
+        <v>1.333565</v>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>yfinance</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8733,7 +9335,7 @@
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
@@ -8741,22 +9343,29 @@
           <t>IWDA.L</t>
         </is>
       </c>
-      <c r="C231" s="5" t="n"/>
+      <c r="C231" s="5" t="n">
+        <v>146.580002</v>
+      </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-10-21</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
@@ -8764,38 +9373,508 @@
           <t>LIGT3.SA</t>
         </is>
       </c>
-      <c r="C232" s="5" t="n"/>
+      <c r="C232" s="5" t="n">
+        <v>3.73</v>
+      </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>yfinance-no-close-on-2026-10-21</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>SAPR11.SA</t>
+        </is>
+      </c>
+      <c r="C233" s="5" t="n">
+        <v>40.049999</v>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>BRLUSD=X</t>
+        </is>
+      </c>
+      <c r="C234" s="5" t="n">
+        <v>0.198531</v>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>CHFUSD=X</t>
+        </is>
+      </c>
+      <c r="C235" s="5" t="n">
+        <v>1.210698</v>
+      </c>
+      <c r="D235" s="2" t="n"/>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>EURUSD=X</t>
+        </is>
+      </c>
+      <c r="C236" s="5" t="n">
+        <v>1.122083</v>
+      </c>
+      <c r="D236" s="2" t="n"/>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP.AT</t>
+        </is>
+      </c>
+      <c r="C237" s="5" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>GBPUSD=X</t>
+        </is>
+      </c>
+      <c r="C238" s="5" t="n">
+        <v>1.33154</v>
+      </c>
+      <c r="D238" s="2" t="n"/>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>IWDA.L</t>
+        </is>
+      </c>
+      <c r="C239" s="5" t="n">
+        <v>146.520004</v>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>LIGT3.SA</t>
+        </is>
+      </c>
+      <c r="C240" s="5" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>SAPR11.SA</t>
+        </is>
+      </c>
+      <c r="C241" s="5" t="n">
+        <v>40.880001</v>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B233" s="2" t="inlineStr">
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>BRLUSD=X</t>
+        </is>
+      </c>
+      <c r="C242" s="5" t="n">
+        <v>0.199191</v>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>CHFUSD=X</t>
+        </is>
+      </c>
+      <c r="C243" s="5" t="n">
+        <v>1.211284</v>
+      </c>
+      <c r="D243" s="2" t="n"/>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>EURUSD=X</t>
+        </is>
+      </c>
+      <c r="C244" s="5" t="n">
+        <v>1.122965</v>
+      </c>
+      <c r="D244" s="2" t="n"/>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP.AT</t>
+        </is>
+      </c>
+      <c r="C245" s="5" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>GBPUSD=X</t>
+        </is>
+      </c>
+      <c r="C246" s="5" t="n">
+        <v>1.337453</v>
+      </c>
+      <c r="D246" s="2" t="n"/>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>IWDA.L</t>
+        </is>
+      </c>
+      <c r="C247" s="5" t="n">
+        <v>147.259995</v>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>LIGT3.SA</t>
+        </is>
+      </c>
+      <c r="C248" s="5" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
         <is>
           <t>SAPR11.SA</t>
         </is>
       </c>
-      <c r="C233" s="5" t="n"/>
-      <c r="D233" s="2" t="inlineStr">
-        <is>
-          <t>yfinance-no-close-on-2026-10-21</t>
-        </is>
-      </c>
-      <c r="E233" s="2" t="inlineStr">
-        <is>
-          <t>missing</t>
+      <c r="C249" s="5" t="n">
+        <v>41.110001</v>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
         </is>
       </c>
     </row>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>101303.98</v>
+        <v>101316.71</v>
       </c>
       <c r="C32" s="3" t="n">
         <v>0</v>
@@ -1965,10 +1965,10 @@
         <v>10.13</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>8871.57</v>
+        <v>8884.299999999999</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>101303.98</v>
+        <v>101316.71</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>0</v>
@@ -1981,19 +1981,19 @@
       </c>
       <c r="J32" s="2" t="n"/>
       <c r="K32" s="4" t="n">
-        <v>0.002217</v>
+        <v>0.002343</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.01304</v>
+        <v>0.013167</v>
       </c>
       <c r="M32" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.011781</v>
+        <v>0.011908</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.008517</v>
+        <v>0.008644000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2477,7 +2477,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>13.94</v>
+        <v>13.96</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>PRICE 13.94 = Boerse Stuttgart quote 21 Oct 2026 as proxy for the ATSE close; replace with the ATSE 21 Oct close once the backfill lands and keep the date</t>
+          <t>ATSE close 21 Oct 2026 per Yahoo (backfill); memo W43 used the Stuttgart quote 13.94 as proxy on decision day</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Exited 2026-10-21 at EUR13.94 (proxy for ATSE close); about +16% in EUR; memos/2026-W43.md</t>
+          <t>Exited 2026-10-21 at EUR13.96 (ATSE close); about +16% in EUR; memos/2026-W43.md</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3105,7 @@
         <v>7992.01</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>8871.57</v>
+        <v>8884.299999999999</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -2007,7 +2007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S4"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2304,6 +2304,73 @@
       <c r="Q4" s="2" t="n"/>
       <c r="R4" s="2" t="n"/>
       <c r="S4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>BASC:LSE</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Brown Advisory US Smaller Companies (investment trust)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>equity</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>watchlist</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Fast</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="5" t="n">
+        <v>1640</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="4" t="n"/>
+      <c r="O5" s="5" t="n">
+        <v>1689</v>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>0.0299</v>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>Entry trigger, not kill: discount &gt;= 5% to last published NAV with scheme on track. If entered: scheme voted down or withdrawn; circular not out by 2026-11-30; discount &lt; 1%</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2556,7 +2623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2763,7 +2830,11 @@
           <t>2026-W37.md</t>
         </is>
       </c>
-      <c r="N3" s="2" t="n"/>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Moro (PL) elected governor 4 Oct 2026, first round, no privatisation commitment; XP neutral 16 Sep; still no dated catalyst; memos/2026-W43-b.md</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2803,7 +2874,7 @@
       <c r="K4" s="2" t="n"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>gated</t>
+          <t>gated (3T26 leverage test)</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -2811,7 +2882,77 @@
           <t>2026-W37.md</t>
         </is>
       </c>
-      <c r="N4" s="2" t="n"/>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>RJ closed 9 Sep 2026; R$1.5bn capital increase done Jul 2026; 2T26 ND/EBITDA 2.85x reported (2.07x ex convertible); emergence test awaits 3T26 balance sheet; memos/2026-W43-b.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Brown Advisory US Smaller Companies</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>BASC:LSE</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>1640</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>1689</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Uncapped cash exit at 99.25% of residual NAV under scheme of reconstruction into JUSC; Saba 16% irrevocable</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Entry trigger: discount &gt;= 5% to last published NAV with scheme on track (net spread then &gt;= 2.5% after the fund cost model). If entered: scheme voted down or withdrawn; circular not out by 2026-11-30; discount &lt; 1%</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>n/a (fast sleeve)</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>watchlist</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2026-W43-b.md</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Not entered: at 1640p vs 1702.25p NAV (15 Oct) the gross spread to the 99.25% cash exit is about 2.6% and the fund cost model on a hedged pair takes about 1.5%; fair spread, not a mispricing</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2824,7 +2965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3010,6 +3151,212 @@
       <c r="F6" s="2" t="inlineStr">
         <is>
           <t>A dated regulatory decision</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Kyocera</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>6971:TSE</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Mechanism exists (JPY500bn KDDI sales FY26-27, JPY200bn buyback FY26, up to JPY500bn more through FY28, Oasis campaign) but no mispricing shown: KDDI stake about JPY1.56tn (13.36% x JPY11.65tn, 18 Sep) against market cap JPY4.69tn leaves the core at about 31x FY26 forecast operating profit of JPY100bn; P/B 1.39</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Core implied value falls below 15x operating profit, or a tender/buyback at a stated discount</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>AVI Japan Opportunity Trust</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>AJOT:LSE</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Uncapped 100% tender at NAV less 2% (RNS 19 Oct 2026) but the record date was 6pm 20 Oct, before this memo; shares bought now cannot tender and the tender itself bounds the discount</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Next annual tender, if the trust survives the GBP100m floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Partners Group Private Equity</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>PGPE:LSE</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Wind-down approved 7 Oct 2026 (about three quarters of holders chose cash) but listed private equity is the salary-correlated exposure the mandate excludes; also no distribution timetable</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>User lifts the factor exclusion by dated amendment</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Edinburgh Worldwide</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>EWI:LSE</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Saba-controlled board promises a tender after the SpaceX IPO (12 Jun 2026) and lock-up expiry (about six months), but the discount was about 1% in June 2026: the closer is priced. Tender terms and date not announced</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Discount wider than 5% with the tender terms published</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Liberty Broadband</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>LBRDK:NASDAQ</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Holdco collapse into Charter completed in August 2026, ten months ahead of the 30 Jun 2027 target. Event over</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Vivendi</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>VIV:EPA</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Paris Court of Appeal ruled 8 Jul 2026 that Bollore does not control Vivendi, so no mandatory offer; holdco discount has no closer; stock fell about 10% that day</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>A distribution of the UMG stake or a buyback at NAV is announced with a date</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Lindsell Train IT</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>LTI:LSE</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>20% tender at NAV less 5% completed 16 Oct 2026; event over; residual discount has no closer</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Next tender announced</t>
         </is>
       </c>
     </row>
@@ -3139,7 +3486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F249"/>
+  <dimension ref="A1:F250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9878,6 +10225,36 @@
         </is>
       </c>
     </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>BASC.L</t>
+        </is>
+      </c>
+      <c r="C250" s="5" t="n">
+        <v>1640</v>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -9662,7 +9662,7 @@
         </is>
       </c>
       <c r="C242" s="5" t="n">
-        <v>0.199191</v>
+        <v>0.199096</v>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
@@ -9692,9 +9692,13 @@
         </is>
       </c>
       <c r="C243" s="5" t="n">
-        <v>1.211284</v>
-      </c>
-      <c r="D243" s="2" t="n"/>
+        <v>1.211196</v>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
           <t>yfinance</t>
@@ -9718,9 +9722,13 @@
         </is>
       </c>
       <c r="C244" s="5" t="n">
-        <v>1.122965</v>
-      </c>
-      <c r="D244" s="2" t="n"/>
+        <v>1.122675</v>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
           <t>yfinance</t>
@@ -9774,9 +9782,13 @@
         </is>
       </c>
       <c r="C246" s="5" t="n">
-        <v>1.337453</v>
-      </c>
-      <c r="D246" s="2" t="n"/>
+        <v>1.337327</v>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
           <t>yfinance</t>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1994,6 +1994,53 @@
       </c>
       <c r="O32" s="4" t="n">
         <v>0.008644000000000001</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>101327.82</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>101327.82</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>-0.010707</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>0.004631</v>
+      </c>
+      <c r="J33" s="2" t="n"/>
+      <c r="K33" s="4" t="n">
+        <v>0.00011</v>
+      </c>
+      <c r="L33" s="4" t="n">
+        <v>0.013278</v>
+      </c>
+      <c r="M33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="4" t="n">
+        <v>0.023985</v>
+      </c>
+      <c r="O33" s="4" t="n">
+        <v>0.008647</v>
       </c>
     </row>
   </sheetData>
@@ -2164,11 +2211,11 @@
       </c>
       <c r="H2" s="3" t="n"/>
       <c r="I2" s="5" t="n">
-        <v>13.96</v>
+        <v>13.8</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="K2" s="3" t="n"/>
@@ -2179,7 +2226,7 @@
         <v>15.3</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>0.096</v>
+        <v>0.1087</v>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
@@ -2187,7 +2234,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -2231,11 +2278,11 @@
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="5" t="n">
-        <v>41.110001</v>
+        <v>41.07</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="K3" s="3" t="n"/>
@@ -2288,11 +2335,11 @@
       </c>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="5" t="n">
-        <v>3.68</v>
+        <v>3.64</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="K4" s="3" t="n"/>
@@ -3139,7 +3186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F249"/>
+  <dimension ref="A1:F257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9890,6 +9937,246 @@
         </is>
       </c>
     </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>BRLUSD=X</t>
+        </is>
+      </c>
+      <c r="C250" s="5" t="n">
+        <v>0.199188</v>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>CHFUSD=X</t>
+        </is>
+      </c>
+      <c r="C251" s="5" t="n">
+        <v>1.213592</v>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F251" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>EURUSD=X</t>
+        </is>
+      </c>
+      <c r="C252" s="5" t="n">
+        <v>1.123469</v>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP.AT</t>
+        </is>
+      </c>
+      <c r="C253" s="5" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F253" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>GBPUSD=X</t>
+        </is>
+      </c>
+      <c r="C254" s="5" t="n">
+        <v>1.339567</v>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F254" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>IWDA.L</t>
+        </is>
+      </c>
+      <c r="C255" s="5" t="n">
+        <v>145.5</v>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>LIGT3.SA</t>
+        </is>
+      </c>
+      <c r="C256" s="5" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>SAPR11.SA</t>
+        </is>
+      </c>
+      <c r="C257" s="5" t="n">
+        <v>41.07</v>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2041,6 +2041,53 @@
       </c>
       <c r="O33" s="4" t="n">
         <v>0.008647</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>101338.92</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>101338.92</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>-0.011251</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>0.004739</v>
+      </c>
+      <c r="J34" s="2" t="n"/>
+      <c r="K34" s="4" t="n">
+        <v>0.00011</v>
+      </c>
+      <c r="L34" s="4" t="n">
+        <v>0.013389</v>
+      </c>
+      <c r="M34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="4" t="n">
+        <v>0.02464</v>
+      </c>
+      <c r="O34" s="4" t="n">
+        <v>0.00865</v>
       </c>
     </row>
   </sheetData>
@@ -2211,11 +2258,11 @@
       </c>
       <c r="H2" s="3" t="n"/>
       <c r="I2" s="5" t="n">
-        <v>13.8</v>
+        <v>13.88</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="K2" s="3" t="n"/>
@@ -2226,7 +2273,7 @@
         <v>15.3</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>0.1087</v>
+        <v>0.1023</v>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
@@ -2234,7 +2281,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -2278,11 +2325,11 @@
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="5" t="n">
-        <v>41.07</v>
+        <v>41.919998</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="K3" s="3" t="n"/>
@@ -2335,11 +2382,11 @@
       </c>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="5" t="n">
-        <v>3.64</v>
+        <v>3.67</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="K4" s="3" t="n"/>
@@ -3186,7 +3233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F257"/>
+  <dimension ref="A1:F265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10177,6 +10224,246 @@
         </is>
       </c>
     </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>BRLUSD=X</t>
+        </is>
+      </c>
+      <c r="C258" s="5" t="n">
+        <v>0.198024</v>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>CHFUSD=X</t>
+        </is>
+      </c>
+      <c r="C259" s="5" t="n">
+        <v>1.219795</v>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>EURUSD=X</t>
+        </is>
+      </c>
+      <c r="C260" s="5" t="n">
+        <v>1.120448</v>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP.AT</t>
+        </is>
+      </c>
+      <c r="C261" s="5" t="n">
+        <v>13.88</v>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>GBPUSD=X</t>
+        </is>
+      </c>
+      <c r="C262" s="5" t="n">
+        <v>1.337489</v>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>IWDA.L</t>
+        </is>
+      </c>
+      <c r="C263" s="5" t="n">
+        <v>145.419998</v>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>LIGT3.SA</t>
+        </is>
+      </c>
+      <c r="C264" s="5" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>SAPR11.SA</t>
+        </is>
+      </c>
+      <c r="C265" s="5" t="n">
+        <v>41.919998</v>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F265" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:O35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2088,6 +2088,53 @@
       </c>
       <c r="O34" s="4" t="n">
         <v>0.00865</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>101372.24</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>33.32</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>101372.24</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>-0.007648</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>0.005063</v>
+      </c>
+      <c r="J35" s="2" t="n"/>
+      <c r="K35" s="4" t="n">
+        <v>0.000329</v>
+      </c>
+      <c r="L35" s="4" t="n">
+        <v>0.013722</v>
+      </c>
+      <c r="M35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="4" t="n">
+        <v>0.02137</v>
+      </c>
+      <c r="O35" s="4" t="n">
+        <v>0.008659</v>
       </c>
     </row>
   </sheetData>
@@ -2258,11 +2305,11 @@
       </c>
       <c r="H2" s="3" t="n"/>
       <c r="I2" s="5" t="n">
-        <v>13.88</v>
+        <v>13.9</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="K2" s="3" t="n"/>
@@ -2273,7 +2320,7 @@
         <v>15.3</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>0.1023</v>
+        <v>0.1007</v>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
@@ -2281,7 +2328,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>-23</v>
+        <v>-26</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -2325,11 +2372,11 @@
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="5" t="n">
-        <v>41.919998</v>
+        <v>34.169998</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="K3" s="3" t="n"/>
@@ -2382,11 +2429,11 @@
       </c>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="5" t="n">
-        <v>3.67</v>
+        <v>2.72</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="K4" s="3" t="n"/>
@@ -3233,7 +3280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F265"/>
+  <dimension ref="A1:F273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10464,6 +10511,246 @@
         </is>
       </c>
     </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>BRLUSD=X</t>
+        </is>
+      </c>
+      <c r="C266" s="5" t="n">
+        <v>0.201605</v>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>CHFUSD=X</t>
+        </is>
+      </c>
+      <c r="C267" s="5" t="n">
+        <v>1.213843</v>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>EURUSD=X</t>
+        </is>
+      </c>
+      <c r="C268" s="5" t="n">
+        <v>1.121755</v>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP.AT</t>
+        </is>
+      </c>
+      <c r="C269" s="5" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>GBPUSD=X</t>
+        </is>
+      </c>
+      <c r="C270" s="5" t="n">
+        <v>1.337775</v>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>IWDA.L</t>
+        </is>
+      </c>
+      <c r="C271" s="5" t="n">
+        <v>145.949997</v>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>LIGT3.SA</t>
+        </is>
+      </c>
+      <c r="C272" s="5" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>SAPR11.SA</t>
+        </is>
+      </c>
+      <c r="C273" s="5" t="n">
+        <v>34.169998</v>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O35"/>
+  <dimension ref="A1:O36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2135,6 +2135,53 @@
       </c>
       <c r="O35" s="4" t="n">
         <v>0.008659</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>101383.35</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>101383.35</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>-0.003024</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>0.005171</v>
+      </c>
+      <c r="J36" s="2" t="n"/>
+      <c r="K36" s="4" t="n">
+        <v>0.00011</v>
+      </c>
+      <c r="L36" s="4" t="n">
+        <v>0.013834</v>
+      </c>
+      <c r="M36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="4" t="n">
+        <v>0.016858</v>
+      </c>
+      <c r="O36" s="4" t="n">
+        <v>0.008663000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2305,11 +2352,11 @@
       </c>
       <c r="H2" s="3" t="n"/>
       <c r="I2" s="5" t="n">
-        <v>13.9</v>
+        <v>13.82</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="K2" s="3" t="n"/>
@@ -2320,7 +2367,7 @@
         <v>15.3</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>0.1007</v>
+        <v>0.1071</v>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
@@ -2328,7 +2375,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -2372,11 +2419,11 @@
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="5" t="n">
-        <v>34.169998</v>
+        <v>33.669998</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="K3" s="3" t="n"/>
@@ -2429,11 +2476,11 @@
       </c>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="5" t="n">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="K4" s="3" t="n"/>
@@ -3280,7 +3327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F273"/>
+  <dimension ref="A1:F281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10751,6 +10798,246 @@
         </is>
       </c>
     </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>BRLUSD=X</t>
+        </is>
+      </c>
+      <c r="C274" s="5" t="n">
+        <v>0.18613</v>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>CHFUSD=X</t>
+        </is>
+      </c>
+      <c r="C275" s="5" t="n">
+        <v>1.208386</v>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F275" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>EURUSD=X</t>
+        </is>
+      </c>
+      <c r="C276" s="5" t="n">
+        <v>1.117381</v>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F276" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP.AT</t>
+        </is>
+      </c>
+      <c r="C277" s="5" t="n">
+        <v>13.82</v>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F277" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>GBPUSD=X</t>
+        </is>
+      </c>
+      <c r="C278" s="5" t="n">
+        <v>1.334508</v>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F278" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>IWDA.L</t>
+        </is>
+      </c>
+      <c r="C279" s="5" t="n">
+        <v>146.630005</v>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F279" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>LIGT3.SA</t>
+        </is>
+      </c>
+      <c r="C280" s="5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F280" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>SAPR11.SA</t>
+        </is>
+      </c>
+      <c r="C281" s="5" t="n">
+        <v>33.669998</v>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F281" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O36"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2184,6 +2184,53 @@
         <v>0.008663000000000001</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>98345.49000000001</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>3036.82</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>-3048.97</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>101382.31</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>-0.003024</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>0.005279</v>
+      </c>
+      <c r="J37" s="2" t="n"/>
+      <c r="K37" s="4" t="n">
+        <v>-1e-05</v>
+      </c>
+      <c r="L37" s="4" t="n">
+        <v>0.013823</v>
+      </c>
+      <c r="M37" s="4" t="n">
+        <v>-1e-05</v>
+      </c>
+      <c r="N37" s="4" t="n">
+        <v>0.016847</v>
+      </c>
+      <c r="O37" s="4" t="n">
+        <v>0.008544</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2195,7 +2242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S4"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2375,7 +2422,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -2492,6 +2539,248 @@
       <c r="Q4" s="2" t="n"/>
       <c r="R4" s="2" t="n"/>
       <c r="S4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>LNZ:VIE</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Lenzing AG</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>equity</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Fast</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>3048.97</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>3036.82</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>-12.15</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="O5" s="5" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>0.2056</v>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-09</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>Q3 EBITDA &lt; EUR90m; further capital/covenant event; user rules hybrids count as debt; mandatory exit 2026-12-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>PNN:LSE</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Pennon Group</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>equity</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>gated</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Fast</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="3" t="n"/>
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="4" t="n"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>n/a until user rules on regulated-utility leverage (memo W44 q1); Yahoo quotes in pence</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>ERA:PAR</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Eramet</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>equity</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>watchlist</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Fast</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="2" t="n"/>
+      <c r="K7" s="3" t="n"/>
+      <c r="L7" s="3" t="n"/>
+      <c r="M7" s="4" t="n"/>
+      <c r="N7" s="4" t="n"/>
+      <c r="O7" s="5" t="n"/>
+      <c r="P7" s="4" t="n"/>
+      <c r="Q7" s="2" t="n"/>
+      <c r="R7" s="2" t="n"/>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>n/a until prospectus; leverage test on prospectus balance sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>YCA:AIM</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Yellow Cake plc</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>equity</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>watchlist</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Fast</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="3" t="n"/>
+      <c r="L8" s="3" t="n"/>
+      <c r="M8" s="4" t="n"/>
+      <c r="N8" s="4" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="4" t="n"/>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>n/a until final list and NAV discount checked; Yahoo quotes in pence</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2504,7 +2793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2688,6 +2977,60 @@
       <c r="L3" s="2" t="inlineStr">
         <is>
           <t>ATSE close 21 Oct 2026 per Yahoo (backfill); memo W43 used the Stuttgart quote 13.94 as proxy on decision day</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>2026-W44</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>LNZ:VIE</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>1.117381</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Stock 29% below TERP (EUR15.04) eight days after a 99%-subscribed 9-for-10 rights issue at EUR8.65; selling was discretionary and ATX flow is a buyer; fast sleeve 3% of NAV</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2026-W44.md</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Vienna close 28 Oct 2026 per boerse-social.com entered as manual row; Yahoo unreachable from routine sandbox; EURUSD 27 Oct feed close</t>
         </is>
       </c>
     </row>
@@ -2744,7 +3087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3001,6 +3344,308 @@
       </c>
       <c r="N4" s="2" t="n"/>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Lenzing</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>LNZ:VIE</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Post-rights overhang clearance (TERP 15.04); Q3 5 Nov</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-09</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Q3 EBITDA &lt; EUR90m; further capital/covenant event; hybrid ruling; mandatory exit 9 Dec</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>n/a (fast sleeve)</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2026-W44.md</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Pennon</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>PNN:LSE</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>352</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Post-rights overhang (TERP 387.73p; rump 330p); H1 results 1 Dec 2026</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>n/a until ruling</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>W48</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>gated</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2026-W44.md</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Gated on leverage exclusion (7.4x ND/EBITDA pro forma); memo W44 q1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Eramet</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>ERA:PAR</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>EUR500m rights issue with State backstop; terms after 29 Oct Q3 release</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>n/a until prospectus</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>watchlist</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2026-W44.md</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Price 26 Oct close (MarketScreener); adjusted leverage 4.5x at H1; entry only during/after rights period</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Yellow Cake</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>YCA:AIM</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>562</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>MSCI non-operating-company deletion; list 11 Nov; effective 30 Nov</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>n/a until list and NAV discount</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>W48</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>watchlist</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2026-W44.md</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Price stale (13 Aug 2026 UNVERIFIED); NAV not retrieved; memo W44 q3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Corteva</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>CTVA:NYSE</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>11.63</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Parent after Vylor spin (1 Oct); S&amp;P 500 to MidCap 400 on 6 Oct; at 52-week low</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="n"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>W48</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>pointer</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2026-W44.md</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Lens-0 pointer for W48; US-situs; price 27 Oct close (stockanalysis.com)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3012,7 +3657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3198,6 +3843,156 @@
       <c r="F6" s="2" t="inlineStr">
         <is>
           <t>A dated regulatory decision</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Genting Berhad</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>GENTING:KLSE</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>RM1.25bn rights issue partly funds interest and short-term debt repayment at a levered holdco; Bursa access at IBKR unverified</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Never while proceeds fund interest</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Raizen</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>RAIZ4:B3</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Distressed recap inside recuperacao extrajudicial; net debt R$60bn vs market cap about R$3bn; Brazil cap; lens-1 question only after conversion</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Post-conversion balance sheet below 2.5x and a dated event</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Unipol Assicurazioni</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>UNI:MIL</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Financial (insurer buying bank branches); stock rose on announcement; no overhang</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Never (financial exclusion)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Strategy / Metaplanet</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>MSTR:NASDAQ and 3350:TSE</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Likely MSCI deletions 30 Nov but leveraged bitcoin holding vehicles; excluded on substance</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Oncoclinicas (follow-up)</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>ONCO3:B3</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>OPA suspended by federal injunction 23 Oct 2026 one day before CVM deadline; merits undecided; no dated event</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Injunction lifted and an edital de OPA with a leilao date</t>
         </is>
       </c>
     </row>
@@ -3327,7 +4122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F281"/>
+  <dimension ref="A1:F282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11038,6 +11833,36 @@
         </is>
       </c>
     </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>LNZ.VI</t>
+        </is>
+      </c>
+      <c r="C282" s="5" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="F282" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O36"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2182,6 +2182,53 @@
       </c>
       <c r="O36" s="4" t="n">
         <v>0.008663000000000001</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>101394.46</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>101394.46</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>-0.001732</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>0.005279</v>
+      </c>
+      <c r="J37" s="2" t="n"/>
+      <c r="K37" s="4" t="n">
+        <v>0.00011</v>
+      </c>
+      <c r="L37" s="4" t="n">
+        <v>0.013945</v>
+      </c>
+      <c r="M37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="4" t="n">
+        <v>0.015677</v>
+      </c>
+      <c r="O37" s="4" t="n">
+        <v>0.008666</v>
       </c>
     </row>
   </sheetData>
@@ -2356,7 +2403,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="K2" s="3" t="n"/>
@@ -2375,7 +2422,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -2419,11 +2466,11 @@
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="5" t="n">
-        <v>33.669998</v>
+        <v>32.419998</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="K3" s="3" t="n"/>
@@ -2476,11 +2523,11 @@
       </c>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="5" t="n">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="K4" s="3" t="n"/>
@@ -3327,7 +3374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F281"/>
+  <dimension ref="A1:F289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11038,6 +11085,246 @@
         </is>
       </c>
     </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>BRLUSD=X</t>
+        </is>
+      </c>
+      <c r="C282" s="5" t="n">
+        <v>0.186905</v>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F282" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>CHFUSD=X</t>
+        </is>
+      </c>
+      <c r="C283" s="5" t="n">
+        <v>1.206564</v>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="E283" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F283" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>EURUSD=X</t>
+        </is>
+      </c>
+      <c r="C284" s="5" t="n">
+        <v>1.112966</v>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F284" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP.AT</t>
+        </is>
+      </c>
+      <c r="C285" s="5" t="n">
+        <v>13.82</v>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F285" s="2" t="inlineStr">
+        <is>
+          <t>lagged</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>GBPUSD=X</t>
+        </is>
+      </c>
+      <c r="C286" s="5" t="n">
+        <v>1.33063</v>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F286" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t>IWDA.L</t>
+        </is>
+      </c>
+      <c r="C287" s="5" t="n">
+        <v>146.820007</v>
+      </c>
+      <c r="D287" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="E287" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F287" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>LIGT3.SA</t>
+        </is>
+      </c>
+      <c r="C288" s="5" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="E288" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F288" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
+        <is>
+          <t>SAPR11.SA</t>
+        </is>
+      </c>
+      <c r="C289" s="5" t="n">
+        <v>32.419998</v>
+      </c>
+      <c r="D289" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="E289" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F289" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O37"/>
+  <dimension ref="A1:O38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2229,6 +2229,53 @@
       </c>
       <c r="O37" s="4" t="n">
         <v>0.008666</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>101405.57</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>101405.57</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>-0.002208</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>0.005387</v>
+      </c>
+      <c r="J38" s="2" t="n"/>
+      <c r="K38" s="4" t="n">
+        <v>0.00011</v>
+      </c>
+      <c r="L38" s="4" t="n">
+        <v>0.014056</v>
+      </c>
+      <c r="M38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="4" t="n">
+        <v>0.016264</v>
+      </c>
+      <c r="O38" s="4" t="n">
+        <v>0.008669</v>
       </c>
     </row>
   </sheetData>
@@ -2399,11 +2446,11 @@
       </c>
       <c r="H2" s="3" t="n"/>
       <c r="I2" s="5" t="n">
-        <v>13.82</v>
+        <v>13.6</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="K2" s="3" t="n"/>
@@ -2414,7 +2461,7 @@
         <v>15.3</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>0.1071</v>
+        <v>0.125</v>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
@@ -2422,7 +2469,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -2466,11 +2513,11 @@
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="5" t="n">
-        <v>32.419998</v>
+        <v>31.85</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="K3" s="3" t="n"/>
@@ -2523,11 +2570,11 @@
       </c>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="5" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="K4" s="3" t="n"/>
@@ -3374,7 +3421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F289"/>
+  <dimension ref="A1:F297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11325,6 +11372,246 @@
         </is>
       </c>
     </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>BRLUSD=X</t>
+        </is>
+      </c>
+      <c r="C290" s="5" t="n">
+        <v>0.187059</v>
+      </c>
+      <c r="D290" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="E290" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F290" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
+        <is>
+          <t>CHFUSD=X</t>
+        </is>
+      </c>
+      <c r="C291" s="5" t="n">
+        <v>1.207802</v>
+      </c>
+      <c r="D291" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="E291" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F291" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>EURUSD=X</t>
+        </is>
+      </c>
+      <c r="C292" s="5" t="n">
+        <v>1.115573</v>
+      </c>
+      <c r="D292" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="E292" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F292" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
+        <is>
+          <t>EYDAP.AT</t>
+        </is>
+      </c>
+      <c r="C293" s="5" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="D293" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="E293" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F293" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>GBPUSD=X</t>
+        </is>
+      </c>
+      <c r="C294" s="5" t="n">
+        <v>1.3328</v>
+      </c>
+      <c r="D294" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F294" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t>IWDA.L</t>
+        </is>
+      </c>
+      <c r="C295" s="5" t="n">
+        <v>146.75</v>
+      </c>
+      <c r="D295" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="E295" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F295" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>LIGT3.SA</t>
+        </is>
+      </c>
+      <c r="C296" s="5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="D296" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="E296" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F296" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <t>SAPR11.SA</t>
+        </is>
+      </c>
+      <c r="C297" s="5" t="n">
+        <v>31.85</v>
+      </c>
+      <c r="D297" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="E297" s="2" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="F297" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
